--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="256">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -717,6 +717,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -5006,7 +5009,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5421,153 +5424,174 @@
         <v>229</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="50">
+        <v>368</v>
+      </c>
+      <c r="D23" s="50">
+        <v>847</v>
+      </c>
+      <c r="E23" s="50">
+        <v>1601</v>
+      </c>
+      <c r="F23" s="50">
+        <v>2506</v>
+      </c>
+      <c r="G23" s="50">
+        <v>3500</v>
+      </c>
+      <c r="H23" s="49" t="s">
         <v>230</v>
       </c>
-      <c r="C24" s="12" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
+      <c r="E25" s="12"/>
+      <c r="F25" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D25" s="56" t="s">
-        <v>236</v>
-      </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="57" t="s">
-        <v>237</v>
-      </c>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="55" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C26" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E26" s="56"/>
       <c r="F26" s="57" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G26" s="57"/>
       <c r="H26" s="57"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E27" s="56"/>
       <c r="F27" s="57" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G27" s="57"/>
       <c r="H27" s="57"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="55" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E28" s="56"/>
       <c r="F28" s="57" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G28" s="57"/>
       <c r="H28" s="57"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="55" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E29" s="56"/>
       <c r="F29" s="57" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G29" s="57"/>
       <c r="H29" s="57"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="55" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E30" s="56"/>
       <c r="F30" s="57" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G30" s="57"/>
       <c r="H30" s="57"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="55" t="s">
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D31" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="56"/>
+      <c r="F31" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="55" t="s">
         <v>254</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="58" t="s">
+      <c r="C33" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -5580,8 +5604,10 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="261">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -678,6 +678,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1003,7 +1018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1076,6 +1091,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5009,7 +5030,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5258,356 +5279,439 @@
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="47">
-        <v>0.320976368159204</v>
-      </c>
-      <c r="D16" s="47">
-        <v>0.2651573145792808</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0.19593146471174963</v>
-      </c>
-      <c r="F16" s="47">
-        <v>0.16427855281000456</v>
-      </c>
-      <c r="G16" s="47">
-        <v>0.14866518593056174</v>
-      </c>
-      <c r="H16" s="49" t="s">
+      <c r="C16" s="50">
+        <v>6671.083333333333</v>
+      </c>
+      <c r="D16" s="50">
+        <v>5497.844772727273</v>
+      </c>
+      <c r="E16" s="50">
+        <v>4331.653334999999</v>
+      </c>
+      <c r="F16" s="50">
+        <v>3831.2072896249997</v>
+      </c>
+      <c r="G16" s="50">
+        <v>3619.5617227167504</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+      <c r="C17" s="45">
+        <v>400</v>
+      </c>
+      <c r="D17" s="45">
+        <v>409.99999999999994</v>
+      </c>
+      <c r="E17" s="45">
+        <v>420.24999999999994</v>
+      </c>
+      <c r="F17" s="45">
+        <v>430.75624999999985</v>
+      </c>
+      <c r="G17" s="45">
+        <v>441.5251562499999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="47">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D17" s="47">
-        <v>0.08829368048281712</v>
-      </c>
-      <c r="E17" s="47">
-        <v>0.06519109194759654</v>
-      </c>
-      <c r="F17" s="47">
-        <v>0.05461656630597211</v>
-      </c>
-      <c r="G17" s="47">
-        <v>0.049387113624071166</v>
-      </c>
-      <c r="H17" s="49" t="s">
+      <c r="C18" s="48">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="48">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="48">
+        <v>910.9354999999999</v>
+      </c>
+      <c r="F18" s="48">
+        <v>781.2734395833334</v>
+      </c>
+      <c r="G18" s="48">
+        <v>723.675110915625</v>
+      </c>
+      <c r="H18" s="49" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="47">
-        <v>0.5021579601990049</v>
-      </c>
-      <c r="D18" s="47">
-        <v>0.5978100819658502</v>
-      </c>
-      <c r="E18" s="47">
-        <v>0.6900052628895259</v>
-      </c>
-      <c r="F18" s="47">
-        <v>0.7321713802566707</v>
-      </c>
-      <c r="G18" s="47">
-        <v>0.7529834819896233</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="50">
-        <v>3</v>
-      </c>
-      <c r="D19" s="50">
-        <v>3</v>
-      </c>
-      <c r="E19" s="50">
-        <v>3</v>
-      </c>
-      <c r="F19" s="50">
-        <v>3</v>
-      </c>
-      <c r="G19" s="50">
-        <v>3</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>224</v>
+      <c r="C19" s="51">
+        <v>6728.916666666667</v>
+      </c>
+      <c r="D19" s="51">
+        <v>8171.927954545451</v>
+      </c>
+      <c r="E19" s="51">
+        <v>9641.659164999997</v>
+      </c>
+      <c r="F19" s="51">
+        <v>10473.48984579166</v>
+      </c>
+      <c r="G19" s="51">
+        <v>11033.554400330122</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="51" t="s">
-        <v>44</v>
+        <v>222</v>
+      </c>
+      <c r="C20" s="47">
+        <v>0.320976368159204</v>
+      </c>
+      <c r="D20" s="47">
+        <v>0.2651573145792808</v>
+      </c>
+      <c r="E20" s="47">
+        <v>0.19593146471174963</v>
+      </c>
+      <c r="F20" s="47">
+        <v>0.16427855281000456</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0.14866518593056174</v>
       </c>
       <c r="H20" s="49" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="47">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D21" s="47">
+        <v>0.08829368048281712</v>
+      </c>
+      <c r="E21" s="47">
+        <v>0.06519109194759654</v>
+      </c>
+      <c r="F21" s="47">
+        <v>0.05461656630597211</v>
+      </c>
+      <c r="G21" s="47">
+        <v>0.049387113624071166</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C21" s="33" t="str">
+      <c r="C22" s="47">
+        <v>0.5021579601990049</v>
+      </c>
+      <c r="D22" s="47">
+        <v>0.5978100819658502</v>
+      </c>
+      <c r="E22" s="47">
+        <v>0.6900052628895259</v>
+      </c>
+      <c r="F22" s="47">
+        <v>0.7321713802566707</v>
+      </c>
+      <c r="G22" s="47">
+        <v>0.7529834819896233</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="52">
+        <v>3</v>
+      </c>
+      <c r="D23" s="52">
+        <v>3</v>
+      </c>
+      <c r="E23" s="52">
+        <v>3</v>
+      </c>
+      <c r="F23" s="52">
+        <v>3</v>
+      </c>
+      <c r="G23" s="52">
+        <v>3</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="33" t="str">
         <f>IF('5-Year Model'!B43&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="52" t="str">
+      <c r="D25" s="54" t="str">
         <f>IF(AND('5-Year Model'!C43&gt;=0,'5-Year Model'!B43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="52" t="str">
+      <c r="E25" s="54" t="str">
         <f>IF(AND('5-Year Model'!D43&gt;=0,'5-Year Model'!C43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="52" t="str">
+      <c r="F25" s="54" t="str">
         <f>IF(AND('5-Year Model'!E43&gt;=0,'5-Year Model'!D43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="52" t="str">
+      <c r="G25" s="54" t="str">
         <f>IF(AND('5-Year Model'!F43&gt;=0,'5-Year Model'!E43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H25" s="49" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="53">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="55">
         <v>12</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D26" s="52">
         <v>28</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E26" s="52">
         <v>53</v>
       </c>
-      <c r="F22" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="24" t="s">
+      <c r="F26" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="G26" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="50">
+      <c r="C27" s="52">
         <v>368</v>
       </c>
-      <c r="D23" s="50">
+      <c r="D27" s="52">
         <v>847</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E27" s="52">
         <v>1601</v>
       </c>
-      <c r="F23" s="50">
+      <c r="F27" s="52">
         <v>2506</v>
       </c>
-      <c r="G23" s="50">
+      <c r="G27" s="52">
         <v>3500</v>
       </c>
-      <c r="H23" s="49" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
+      <c r="H27" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="33" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="C29" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57" t="s">
+      <c r="D29" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C27" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D27" s="56" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57" t="s">
+      <c r="C30" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="55" t="s">
+      <c r="D30" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="C28" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D28" s="56" t="s">
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57" t="s">
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="C31" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D29" s="56" t="s">
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
         <v>246</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57" t="s">
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
+      <c r="C32" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D30" s="56" t="s">
+      <c r="E32" s="58"/>
+      <c r="F32" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="E30" s="56"/>
-      <c r="F30" s="57" t="s">
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="55" t="s">
+      <c r="C33" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="58" t="s">
         <v>251</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D31" s="56" t="s">
+      <c r="E33" s="58"/>
+      <c r="F33" s="59" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="56"/>
-      <c r="F31" s="57" t="s">
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
+      <c r="C34" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="E34" s="58"/>
+      <c r="F34" s="59" t="s">
         <v>255</v>
       </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="58"/>
+      <c r="F35" s="59" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="57" t="s">
+        <v>259</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -5653,37 +5757,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="255">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -680,21 +680,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -732,9 +717,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1018,7 +1000,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1091,12 +1073,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5030,7 +5006,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5279,439 +5255,333 @@
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="50">
-        <v>6671.083333333333</v>
-      </c>
-      <c r="D16" s="50">
-        <v>5497.844772727273</v>
-      </c>
-      <c r="E16" s="50">
-        <v>4331.653334999999</v>
-      </c>
-      <c r="F16" s="50">
-        <v>3831.2072896249997</v>
-      </c>
-      <c r="G16" s="50">
-        <v>3619.5617227167504</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="C16" s="47">
+        <v>0.320976368159204</v>
+      </c>
+      <c r="D16" s="47">
+        <v>0.2651573145792808</v>
+      </c>
+      <c r="E16" s="47">
+        <v>0.19593146471174963</v>
+      </c>
+      <c r="F16" s="47">
+        <v>0.16427855281000456</v>
+      </c>
+      <c r="G16" s="47">
+        <v>0.14866518593056174</v>
+      </c>
+      <c r="H16" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="45">
-        <v>400</v>
-      </c>
-      <c r="D17" s="45">
-        <v>409.99999999999994</v>
-      </c>
-      <c r="E17" s="45">
-        <v>420.24999999999994</v>
-      </c>
-      <c r="F17" s="45">
-        <v>430.75624999999985</v>
-      </c>
-      <c r="G17" s="45">
-        <v>441.5251562499999</v>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="47">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D17" s="47">
+        <v>0.08829368048281712</v>
+      </c>
+      <c r="E17" s="47">
+        <v>0.06519109194759654</v>
+      </c>
+      <c r="F17" s="47">
+        <v>0.05461656630597211</v>
+      </c>
+      <c r="G17" s="47">
+        <v>0.049387113624071166</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="48">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="48">
-        <v>1206.9545454545455</v>
-      </c>
-      <c r="E18" s="48">
-        <v>910.9354999999999</v>
-      </c>
-      <c r="F18" s="48">
-        <v>781.2734395833334</v>
-      </c>
-      <c r="G18" s="48">
-        <v>723.675110915625</v>
+      <c r="B18" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" s="47">
+        <v>0.5021579601990049</v>
+      </c>
+      <c r="D18" s="47">
+        <v>0.5978100819658502</v>
+      </c>
+      <c r="E18" s="47">
+        <v>0.6900052628895259</v>
+      </c>
+      <c r="F18" s="47">
+        <v>0.7321713802566707</v>
+      </c>
+      <c r="G18" s="47">
+        <v>0.7529834819896233</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="51">
-        <v>6728.916666666667</v>
-      </c>
-      <c r="D19" s="51">
-        <v>8171.927954545451</v>
-      </c>
-      <c r="E19" s="51">
-        <v>9641.659164999997</v>
-      </c>
-      <c r="F19" s="51">
-        <v>10473.48984579166</v>
-      </c>
-      <c r="G19" s="51">
-        <v>11033.554400330122</v>
+        <v>223</v>
+      </c>
+      <c r="C19" s="50">
+        <v>3</v>
+      </c>
+      <c r="D19" s="50">
+        <v>3</v>
+      </c>
+      <c r="E19" s="50">
+        <v>3</v>
+      </c>
+      <c r="F19" s="50">
+        <v>3</v>
+      </c>
+      <c r="G19" s="50">
+        <v>3</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="47">
-        <v>0.320976368159204</v>
-      </c>
-      <c r="D20" s="47">
-        <v>0.2651573145792808</v>
-      </c>
-      <c r="E20" s="47">
-        <v>0.19593146471174963</v>
-      </c>
-      <c r="F20" s="47">
-        <v>0.16427855281000456</v>
-      </c>
-      <c r="G20" s="47">
-        <v>0.14866518593056174</v>
+        <v>225</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>44</v>
       </c>
       <c r="H20" s="49" t="s">
-        <v>223</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="C21" s="47">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D21" s="47">
-        <v>0.08829368048281712</v>
-      </c>
-      <c r="E21" s="47">
-        <v>0.06519109194759654</v>
-      </c>
-      <c r="F21" s="47">
-        <v>0.05461656630597211</v>
-      </c>
-      <c r="G21" s="47">
-        <v>0.049387113624071166</v>
+        <v>226</v>
+      </c>
+      <c r="C21" s="33" t="str">
+        <f>IF('5-Year Model'!B43&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="52" t="str">
+        <f>IF(AND('5-Year Model'!C43&gt;=0,'5-Year Model'!B43&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="52" t="str">
+        <f>IF(AND('5-Year Model'!D43&gt;=0,'5-Year Model'!C43&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="52" t="str">
+        <f>IF(AND('5-Year Model'!E43&gt;=0,'5-Year Model'!D43&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="52" t="str">
+        <f>IF(AND('5-Year Model'!F43&gt;=0,'5-Year Model'!E43&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="49" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C22" s="47">
-        <v>0.5021579601990049</v>
-      </c>
-      <c r="D22" s="47">
-        <v>0.5978100819658502</v>
-      </c>
-      <c r="E22" s="47">
-        <v>0.6900052628895259</v>
-      </c>
-      <c r="F22" s="47">
-        <v>0.7321713802566707</v>
-      </c>
-      <c r="G22" s="47">
-        <v>0.7529834819896233</v>
+        <v>227</v>
+      </c>
+      <c r="C22" s="53">
+        <v>12</v>
+      </c>
+      <c r="D22" s="50">
+        <v>28</v>
+      </c>
+      <c r="E22" s="50">
+        <v>53</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="54" t="s">
+        <v>228</v>
       </c>
       <c r="H22" s="49" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" s="52">
-        <v>3</v>
-      </c>
-      <c r="D23" s="52">
-        <v>3</v>
-      </c>
-      <c r="E23" s="52">
-        <v>3</v>
-      </c>
-      <c r="F23" s="52">
-        <v>3</v>
-      </c>
-      <c r="G23" s="52">
-        <v>3</v>
-      </c>
-      <c r="H23" s="49" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="24" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
+      <c r="C24" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C25" s="33" t="str">
-        <f>IF('5-Year Model'!B43&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!C43&gt;=0,'5-Year Model'!B43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!D43&gt;=0,'5-Year Model'!C43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!E43&gt;=0,'5-Year Model'!D43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!F43&gt;=0,'5-Year Model'!E43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
+      <c r="D24" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="C26" s="55">
-        <v>12</v>
-      </c>
-      <c r="D26" s="52">
-        <v>28</v>
-      </c>
-      <c r="E26" s="52">
-        <v>53</v>
-      </c>
-      <c r="F26" s="56" t="s">
+      <c r="E24" s="12"/>
+      <c r="F24" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="G26" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="H26" s="49" t="s">
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="55" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" s="52">
-        <v>368</v>
-      </c>
-      <c r="D27" s="52">
-        <v>847</v>
-      </c>
-      <c r="E27" s="52">
-        <v>1601</v>
-      </c>
-      <c r="F27" s="52">
-        <v>2506</v>
-      </c>
-      <c r="G27" s="52">
-        <v>3500</v>
-      </c>
-      <c r="H27" s="49" t="s">
+      <c r="C25" s="33" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="12" t="s">
+      <c r="D25" s="56" t="s">
         <v>236</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="E25" s="56"/>
+      <c r="F25" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="55" t="s">
         <v>238</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12" t="s">
+      <c r="C26" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D26" s="56" t="s">
         <v>239</v>
       </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D27" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="E27" s="56"/>
+      <c r="F27" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="55" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="E28" s="56"/>
+      <c r="F28" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="E29" s="56"/>
+      <c r="F29" s="57" t="s">
+        <v>249</v>
+      </c>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
-        <v>240</v>
+      <c r="B30" s="55" t="s">
+        <v>250</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D31" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
-        <v>246</v>
-      </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="57" t="s">
-        <v>247</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="E32" s="58"/>
-      <c r="F32" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D33" s="58" t="s">
+        <v>235</v>
+      </c>
+      <c r="D30" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="E33" s="58"/>
-      <c r="F33" s="59" t="s">
+      <c r="E30" s="56"/>
+      <c r="F30" s="57" t="s">
         <v>252</v>
       </c>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="57" t="s">
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="55" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D34" s="58" t="s">
+      <c r="C32" s="24" t="s">
         <v>254</v>
       </c>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="58"/>
-      <c r="F34" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="E35" s="58"/>
-      <c r="F35" s="59" t="s">
-        <v>258</v>
-      </c>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B34:H34"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -5757,37 +5627,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="261">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -680,6 +680,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -717,6 +732,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1000,7 +1018,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1073,6 +1091,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -5006,7 +5030,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
+  <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5255,333 +5279,439 @@
         <v>216</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="C16" s="47">
-        <v>0.320976368159204</v>
-      </c>
-      <c r="D16" s="47">
-        <v>0.2651573145792808</v>
-      </c>
-      <c r="E16" s="47">
-        <v>0.19593146471174963</v>
-      </c>
-      <c r="F16" s="47">
-        <v>0.16427855281000456</v>
-      </c>
-      <c r="G16" s="47">
-        <v>0.14866518593056174</v>
-      </c>
-      <c r="H16" s="49" t="s">
+      <c r="C16" s="50">
+        <v>6671.083333333333</v>
+      </c>
+      <c r="D16" s="50">
+        <v>5497.844772727273</v>
+      </c>
+      <c r="E16" s="50">
+        <v>4331.653334999999</v>
+      </c>
+      <c r="F16" s="50">
+        <v>3831.2072896249997</v>
+      </c>
+      <c r="G16" s="50">
+        <v>3619.5617227167504</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+      <c r="C17" s="45">
+        <v>400</v>
+      </c>
+      <c r="D17" s="45">
+        <v>409.99999999999994</v>
+      </c>
+      <c r="E17" s="45">
+        <v>420.24999999999994</v>
+      </c>
+      <c r="F17" s="45">
+        <v>430.75624999999985</v>
+      </c>
+      <c r="G17" s="45">
+        <v>441.5251562499999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="47">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D17" s="47">
-        <v>0.08829368048281712</v>
-      </c>
-      <c r="E17" s="47">
-        <v>0.06519109194759654</v>
-      </c>
-      <c r="F17" s="47">
-        <v>0.05461656630597211</v>
-      </c>
-      <c r="G17" s="47">
-        <v>0.049387113624071166</v>
-      </c>
-      <c r="H17" s="49" t="s">
+      <c r="C18" s="48">
+        <v>1720</v>
+      </c>
+      <c r="D18" s="48">
+        <v>1206.9545454545455</v>
+      </c>
+      <c r="E18" s="48">
+        <v>910.9354999999999</v>
+      </c>
+      <c r="F18" s="48">
+        <v>781.2734395833334</v>
+      </c>
+      <c r="G18" s="48">
+        <v>723.675110915625</v>
+      </c>
+      <c r="H18" s="49" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="47">
-        <v>0.5021579601990049</v>
-      </c>
-      <c r="D18" s="47">
-        <v>0.5978100819658502</v>
-      </c>
-      <c r="E18" s="47">
-        <v>0.6900052628895259</v>
-      </c>
-      <c r="F18" s="47">
-        <v>0.7321713802566707</v>
-      </c>
-      <c r="G18" s="47">
-        <v>0.7529834819896233</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="50">
-        <v>3</v>
-      </c>
-      <c r="D19" s="50">
-        <v>3</v>
-      </c>
-      <c r="E19" s="50">
-        <v>3</v>
-      </c>
-      <c r="F19" s="50">
-        <v>3</v>
-      </c>
-      <c r="G19" s="50">
-        <v>3</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>224</v>
+      <c r="C19" s="51">
+        <v>6728.916666666667</v>
+      </c>
+      <c r="D19" s="51">
+        <v>8171.927954545451</v>
+      </c>
+      <c r="E19" s="51">
+        <v>9641.659164999997</v>
+      </c>
+      <c r="F19" s="51">
+        <v>10473.48984579166</v>
+      </c>
+      <c r="G19" s="51">
+        <v>11033.554400330122</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="51" t="s">
-        <v>44</v>
+        <v>222</v>
+      </c>
+      <c r="C20" s="47">
+        <v>0.320976368159204</v>
+      </c>
+      <c r="D20" s="47">
+        <v>0.2651573145792808</v>
+      </c>
+      <c r="E20" s="47">
+        <v>0.19593146471174963</v>
+      </c>
+      <c r="F20" s="47">
+        <v>0.16427855281000456</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0.14866518593056174</v>
       </c>
       <c r="H20" s="49" t="s">
-        <v>44</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="47">
+        <v>0.12835820895522387</v>
+      </c>
+      <c r="D21" s="47">
+        <v>0.08829368048281712</v>
+      </c>
+      <c r="E21" s="47">
+        <v>0.06519109194759654</v>
+      </c>
+      <c r="F21" s="47">
+        <v>0.05461656630597211</v>
+      </c>
+      <c r="G21" s="47">
+        <v>0.049387113624071166</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C21" s="33" t="str">
+      <c r="C22" s="47">
+        <v>0.5021579601990049</v>
+      </c>
+      <c r="D22" s="47">
+        <v>0.5978100819658502</v>
+      </c>
+      <c r="E22" s="47">
+        <v>0.6900052628895259</v>
+      </c>
+      <c r="F22" s="47">
+        <v>0.7321713802566707</v>
+      </c>
+      <c r="G22" s="47">
+        <v>0.7529834819896233</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" s="52">
+        <v>3</v>
+      </c>
+      <c r="D23" s="52">
+        <v>3</v>
+      </c>
+      <c r="E23" s="52">
+        <v>3</v>
+      </c>
+      <c r="F23" s="52">
+        <v>3</v>
+      </c>
+      <c r="G23" s="52">
+        <v>3</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="C25" s="33" t="str">
         <f>IF('5-Year Model'!B43&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="52" t="str">
+      <c r="D25" s="54" t="str">
         <f>IF(AND('5-Year Model'!C43&gt;=0,'5-Year Model'!B43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="52" t="str">
+      <c r="E25" s="54" t="str">
         <f>IF(AND('5-Year Model'!D43&gt;=0,'5-Year Model'!C43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="52" t="str">
+      <c r="F25" s="54" t="str">
         <f>IF(AND('5-Year Model'!E43&gt;=0,'5-Year Model'!D43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="52" t="str">
+      <c r="G25" s="54" t="str">
         <f>IF(AND('5-Year Model'!F43&gt;=0,'5-Year Model'!E43&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H25" s="49" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="53">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C26" s="55">
         <v>12</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D26" s="52">
         <v>28</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E26" s="52">
         <v>53</v>
       </c>
-      <c r="F22" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" s="54" t="s">
-        <v>228</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12" t="s">
+      <c r="F26" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="55" t="s">
+      <c r="G26" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="H26" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="C25" s="33" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="52">
+        <v>368</v>
+      </c>
+      <c r="D27" s="52">
+        <v>847</v>
+      </c>
+      <c r="E27" s="52">
+        <v>1601</v>
+      </c>
+      <c r="F27" s="52">
+        <v>2506</v>
+      </c>
+      <c r="G27" s="52">
+        <v>3500</v>
+      </c>
+      <c r="H27" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="D25" s="56" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="E25" s="56"/>
-      <c r="F25" s="57" t="s">
+      <c r="C29" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="55" t="s">
+      <c r="D29" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C26" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D26" s="56" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="57" t="s">
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="55" t="s">
+      <c r="C30" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D27" s="56" t="s">
+      <c r="D30" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="E27" s="56"/>
-      <c r="F27" s="57" t="s">
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
         <v>243</v>
       </c>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="55" t="s">
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="C28" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D28" s="56" t="s">
+      <c r="C31" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="56"/>
-      <c r="F28" s="57" t="s">
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
         <v>246</v>
       </c>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="55" t="s">
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="C29" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D29" s="56" t="s">
+      <c r="C32" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D32" s="58" t="s">
         <v>248</v>
       </c>
-      <c r="E29" s="56"/>
-      <c r="F29" s="57" t="s">
+      <c r="E32" s="58"/>
+      <c r="F32" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="55" t="s">
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
         <v>250</v>
       </c>
-      <c r="C30" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="D30" s="56" t="s">
+      <c r="C33" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D33" s="58" t="s">
         <v>251</v>
       </c>
-      <c r="E30" s="56"/>
-      <c r="F30" s="57" t="s">
+      <c r="E33" s="58"/>
+      <c r="F33" s="59" t="s">
         <v>252</v>
       </c>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="55" t="s">
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="57" t="s">
         <v>253</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C34" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="58" t="s">
         <v>254</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="58" t="s">
+      <c r="E34" s="58"/>
+      <c r="F34" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>257</v>
+      </c>
+      <c r="E35" s="58"/>
+      <c r="F35" s="59" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="57" t="s">
+        <v>259</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -5627,37 +5757,37 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -13,11 +13,11 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Instructions'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A1:$J53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Assumptions'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'5-Year Model'!$A1:$F74</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="267">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · llc_single</t>
+    <t>Generated April 29, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -344,6 +344,12 @@
     <t>Insurance</t>
   </si>
   <si>
+    <t>Compliance Contract</t>
+  </si>
+  <si>
+    <t>Administrative / General</t>
+  </si>
+  <si>
     <t>Curriculum &amp; Materials</t>
   </si>
   <si>
@@ -401,6 +407,9 @@
     <t>Liberty Learning Co-Op - 5-Year Financial Model</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>REVENUE</t>
   </si>
   <si>
@@ -443,6 +452,12 @@
     <t>Total Occupancy / Facility</t>
   </si>
   <si>
+    <t xml:space="preserve">  Compliance Contract (Annual Fixed)</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
     <t>TOTAL OPERATING EXPENSES</t>
   </si>
   <si>
@@ -512,7 +527,7 @@
     <t>COVENANT &amp; HEALTH CHECKS</t>
   </si>
   <si>
-    <t>DSCR ≥ 1.20x</t>
+    <t>DSCR ≥ 1.25x</t>
   </si>
   <si>
     <t>Positive Net Income</t>
@@ -599,6 +614,9 @@
     <t xml:space="preserve">  Insurance</t>
   </si>
   <si>
+    <t xml:space="preserve">  Compliance Contract</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
@@ -623,7 +641,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -782,7 +800,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 5% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -800,7 +818,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>115.1 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>115.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -823,7 +841,7 @@
     <numFmt numFmtId="167" formatCode="0.00x"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -885,6 +903,12 @@
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1018,7 +1042,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1048,75 +1072,76 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1810,7 +1835,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2327,10 +2352,10 @@
         <v>106</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D39" s="18">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="E39" s="19">
         <v>0</v>
@@ -2344,13 +2369,13 @@
         <v>107</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>69</v>
       </c>
       <c r="D40" s="18">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E40" s="19">
         <v>0</v>
@@ -2359,107 +2384,127 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B42" s="12" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="B41" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D41" s="18">
+        <v>250</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="F42" s="12" t="s">
+      <c r="D43" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="E43" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="F43" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H43" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B45" s="19">
-        <v>0.03</v>
-      </c>
+    <row r="45" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="19">
         <v>0.025</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B47" s="20">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="B48" s="19">
-        <v>0.03</v>
+      <c r="B48" s="20">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B49" s="19">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
+      <c r="B50" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A53:G53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -2475,7 +2520,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -2484,7 +2529,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2492,1225 +2537,1286 @@
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C3" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F3" s="24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B4" s="26">
         <f>Assumptions!B17</f>
         <v>15</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C4" s="26">
         <f>Assumptions!C17</f>
         <v>22</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D4" s="26">
         <f>Assumptions!D17</f>
         <v>30</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E4" s="26">
         <f>Assumptions!E17</f>
         <v>36</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F4" s="26">
         <f>Assumptions!F17</f>
         <v>40</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="26">
-        <v>75000</v>
-      </c>
-      <c r="C6" s="26">
-        <v>135300</v>
-      </c>
-      <c r="D6" s="26">
-        <v>189112</v>
-      </c>
-      <c r="E6" s="26">
-        <v>232608</v>
-      </c>
-      <c r="F6" s="26">
-        <v>264915</v>
-      </c>
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="26">
-        <v>2500</v>
-      </c>
-      <c r="C7" s="26">
-        <v>4510</v>
-      </c>
-      <c r="D7" s="26">
-        <v>6304</v>
-      </c>
-      <c r="E7" s="26">
-        <v>7754</v>
-      </c>
-      <c r="F7" s="26">
-        <v>8831</v>
+        <v>67</v>
+      </c>
+      <c r="B7" s="27">
+        <v>75000</v>
+      </c>
+      <c r="C7" s="27">
+        <v>135300</v>
+      </c>
+      <c r="D7" s="27">
+        <v>189112</v>
+      </c>
+      <c r="E7" s="27">
+        <v>232608</v>
+      </c>
+      <c r="F7" s="27">
+        <v>264915</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="26">
-        <v>87500</v>
-      </c>
-      <c r="C8" s="26">
-        <v>157850</v>
-      </c>
-      <c r="D8" s="26">
-        <v>220631</v>
-      </c>
-      <c r="E8" s="26">
-        <v>271376</v>
-      </c>
-      <c r="F8" s="26">
-        <v>309068</v>
+        <v>70</v>
+      </c>
+      <c r="B8" s="27">
+        <v>2500</v>
+      </c>
+      <c r="C8" s="27">
+        <v>4510</v>
+      </c>
+      <c r="D8" s="27">
+        <v>6304</v>
+      </c>
+      <c r="E8" s="27">
+        <v>7754</v>
+      </c>
+      <c r="F8" s="27">
+        <v>8831</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="27">
+        <v>87500</v>
+      </c>
+      <c r="C9" s="27">
+        <v>157850</v>
+      </c>
+      <c r="D9" s="27">
+        <v>220631</v>
+      </c>
+      <c r="E9" s="27">
+        <v>271376</v>
+      </c>
+      <c r="F9" s="27">
+        <v>309068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B10" s="27">
         <v>2500</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C10" s="27">
         <v>3075</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D10" s="27">
         <v>3152</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E10" s="27">
         <v>3231</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F10" s="27">
         <v>3311</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B10" s="27">
-        <f>SUM(B6:B9)</f>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="28">
+        <f>SUM(B7:B10)</f>
         <v>167500</v>
       </c>
-      <c r="C10" s="27">
-        <f>SUM(C6:C9)</f>
-        <v>300735</v>
-      </c>
-      <c r="D10" s="27">
-        <f>SUM(D6:D9)</f>
-        <v>419199</v>
-      </c>
-      <c r="E10" s="27">
-        <f>SUM(E6:E9)</f>
-        <v>514969</v>
-      </c>
-      <c r="F10" s="27">
-        <f>SUM(F6:F9)</f>
-        <v>586125</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="26">
-        <v>51060</v>
-      </c>
-      <c r="C13" s="26">
-        <v>63110</v>
-      </c>
-      <c r="D13" s="26">
-        <v>65003</v>
-      </c>
-      <c r="E13" s="26">
-        <v>66954</v>
-      </c>
-      <c r="F13" s="26">
-        <v>68962</v>
-      </c>
+      <c r="C11" s="28">
+        <f>SUM(C7:C10)</f>
+        <v>300625</v>
+      </c>
+      <c r="D11" s="28">
+        <f>SUM(D7:D10)</f>
+        <v>418896</v>
+      </c>
+      <c r="E11" s="28">
+        <f>SUM(E7:E10)</f>
+        <v>514415</v>
+      </c>
+      <c r="F11" s="28">
+        <f>SUM(F7:F10)</f>
+        <v>585294</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="B14" s="26">
+        <v>130</v>
+      </c>
+      <c r="B14" s="27">
+        <v>51060</v>
+      </c>
+      <c r="C14" s="27">
+        <v>63110</v>
+      </c>
+      <c r="D14" s="27">
+        <v>65003</v>
+      </c>
+      <c r="E14" s="27">
+        <v>66954</v>
+      </c>
+      <c r="F14" s="27">
+        <v>68962</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="27">
         <v>13456</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C15" s="27">
         <v>16632</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D15" s="27">
         <v>17131</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E15" s="27">
         <v>17645</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F15" s="27">
         <v>18174</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="27">
-        <f>SUM(B13:B14)</f>
+    <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="28">
+        <f>SUM(B14:B15)</f>
         <v>64516</v>
       </c>
-      <c r="C15" s="27">
-        <f>SUM(C13:C14)</f>
+      <c r="C16" s="28">
+        <f>SUM(C14:C15)</f>
         <v>79742</v>
       </c>
-      <c r="D15" s="27">
-        <f>SUM(D13:D14)</f>
+      <c r="D16" s="28">
+        <f>SUM(D14:D15)</f>
         <v>82134</v>
       </c>
-      <c r="E15" s="27">
-        <f>SUM(E13:E14)</f>
+      <c r="E16" s="28">
+        <f>SUM(E14:E15)</f>
         <v>84598</v>
       </c>
-      <c r="F15" s="27">
-        <f>SUM(F13:F14)</f>
+      <c r="F16" s="28">
+        <f>SUM(F14:F15)</f>
         <v>87136</v>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" s="26">
+        <v>108</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="27">
         <v>5000</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C20" s="27">
         <v>9020</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D20" s="27">
         <v>12607</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E20" s="27">
         <v>15507</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F20" s="27">
         <v>17661</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="29">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="30">
         <v>5000</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="30">
         <v>9020</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D21" s="30">
         <v>12607</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E21" s="30">
         <v>15507</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F21" s="30">
         <v>17661</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="26">
+        <v>109</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="27">
         <v>3125</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C23" s="27">
         <v>5638</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D23" s="27">
         <v>7880</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E23" s="27">
         <v>9692</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F23" s="27">
         <v>11038</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="29">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="30">
         <v>3125</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="30">
         <v>5638</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D24" s="30">
         <v>7880</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E24" s="30">
         <v>9692</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F24" s="30">
         <v>11038</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B25" s="26">
-        <v>18000</v>
-      </c>
-      <c r="C25" s="26">
-        <v>22248</v>
-      </c>
-      <c r="D25" s="26">
-        <v>22915</v>
-      </c>
-      <c r="E25" s="26">
-        <v>23603</v>
-      </c>
-      <c r="F25" s="26">
-        <v>24311</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" s="26">
-        <v>2000</v>
-      </c>
-      <c r="C26" s="26">
-        <v>2460</v>
-      </c>
-      <c r="D26" s="26">
-        <v>2521</v>
-      </c>
-      <c r="E26" s="26">
-        <v>2585</v>
-      </c>
-      <c r="F26" s="26">
-        <v>2649</v>
+        <v>137</v>
+      </c>
+      <c r="B26" s="27">
+        <v>18000</v>
+      </c>
+      <c r="C26" s="27">
+        <v>22248</v>
+      </c>
+      <c r="D26" s="27">
+        <v>22915</v>
+      </c>
+      <c r="E26" s="27">
+        <v>23603</v>
+      </c>
+      <c r="F26" s="27">
+        <v>24311</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="26">
+        <v>138</v>
+      </c>
+      <c r="B27" s="27">
+        <v>2000</v>
+      </c>
+      <c r="C27" s="27">
+        <v>2460</v>
+      </c>
+      <c r="D27" s="27">
+        <v>2521</v>
+      </c>
+      <c r="E27" s="27">
+        <v>2585</v>
+      </c>
+      <c r="F27" s="27">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="27">
         <v>1500</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C28" s="27">
         <v>1845</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D28" s="27">
         <v>1891</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E28" s="27">
         <v>1938</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F28" s="27">
         <v>1987</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="29">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="30">
         <v>21500</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="30">
         <v>26553</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D29" s="30">
         <v>27327</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E29" s="30">
         <v>28126</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F29" s="30">
         <v>28947</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="27">
-        <f>B20+B23+B28</f>
-        <v>29625</v>
-      </c>
-      <c r="C29" s="27">
-        <f>C20+C23+C28</f>
-        <v>41211</v>
-      </c>
-      <c r="D29" s="27">
-        <f>D20+D23+D28</f>
-        <v>47815</v>
-      </c>
-      <c r="E29" s="27">
-        <f>E20+E23+E28</f>
-        <v>53325</v>
-      </c>
-      <c r="F29" s="27">
-        <f>F20+F23+F28</f>
-        <v>57646</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B32" s="27">
-        <v>0</v>
-      </c>
-      <c r="C32" s="27">
-        <v>0</v>
-      </c>
-      <c r="D32" s="27">
-        <v>0</v>
-      </c>
-      <c r="E32" s="27">
-        <v>0</v>
-      </c>
-      <c r="F32" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
+      <c r="B31" s="27">
+        <v>3750</v>
+      </c>
+      <c r="C31" s="27">
+        <v>4613</v>
+      </c>
+      <c r="D31" s="27">
+        <v>4728</v>
+      </c>
+      <c r="E31" s="27">
+        <v>4846</v>
+      </c>
+      <c r="F31" s="27">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="29">
-        <f>B10</f>
+      <c r="B32" s="30">
+        <v>3750</v>
+      </c>
+      <c r="C32" s="30">
+        <v>4613</v>
+      </c>
+      <c r="D32" s="30">
+        <v>4728</v>
+      </c>
+      <c r="E32" s="30">
+        <v>4846</v>
+      </c>
+      <c r="F32" s="30">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" s="28">
+        <f>B21+B24+B29+B32</f>
+        <v>33375</v>
+      </c>
+      <c r="C33" s="28">
+        <f>C21+C24+C29+C32</f>
+        <v>45711</v>
+      </c>
+      <c r="D33" s="28">
+        <f>D21+D24+D29+D32</f>
+        <v>52315</v>
+      </c>
+      <c r="E33" s="28">
+        <f>E21+E24+E29+E32</f>
+        <v>57825</v>
+      </c>
+      <c r="F33" s="28">
+        <f>F21+F24+F29+F32</f>
+        <v>62146</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B36" s="28">
+        <v>0</v>
+      </c>
+      <c r="C36" s="28">
+        <v>0</v>
+      </c>
+      <c r="D36" s="28">
+        <v>0</v>
+      </c>
+      <c r="E36" s="28">
+        <v>0</v>
+      </c>
+      <c r="F36" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" s="30">
+        <f>B11</f>
         <v>167500</v>
       </c>
-      <c r="C35" s="29">
-        <f>C10</f>
-        <v>300735</v>
-      </c>
-      <c r="D35" s="29">
-        <f>D10</f>
-        <v>419199</v>
-      </c>
-      <c r="E35" s="29">
-        <f>E10</f>
-        <v>514969</v>
-      </c>
-      <c r="F35" s="29">
-        <f>F10</f>
-        <v>586125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B36" s="26">
-        <f>B15</f>
+      <c r="C39" s="30">
+        <f>C11</f>
+        <v>300625</v>
+      </c>
+      <c r="D39" s="30">
+        <f>D11</f>
+        <v>418896</v>
+      </c>
+      <c r="E39" s="30">
+        <f>E11</f>
+        <v>514415</v>
+      </c>
+      <c r="F39" s="30">
+        <f>F11</f>
+        <v>585294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="27">
+        <f>B16</f>
         <v>64516</v>
       </c>
-      <c r="C36" s="26">
-        <f>C15</f>
+      <c r="C40" s="27">
+        <f>C16</f>
         <v>79742</v>
       </c>
-      <c r="D36" s="26">
-        <f>D15</f>
+      <c r="D40" s="27">
+        <f>D16</f>
         <v>82134</v>
       </c>
-      <c r="E36" s="26">
-        <f>E15</f>
+      <c r="E40" s="27">
+        <f>E16</f>
         <v>84598</v>
       </c>
-      <c r="F36" s="26">
-        <f>F15</f>
+      <c r="F40" s="27">
+        <f>F16</f>
         <v>87136</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="26">
-        <f>B29</f>
-        <v>29625</v>
-      </c>
-      <c r="C37" s="26">
-        <f>C29</f>
-        <v>41211</v>
-      </c>
-      <c r="D37" s="26">
-        <f>D29</f>
-        <v>47815</v>
-      </c>
-      <c r="E37" s="26">
-        <f>E29</f>
-        <v>53325</v>
-      </c>
-      <c r="F37" s="26">
-        <f>F29</f>
-        <v>57646</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B38" s="26" t="str">
-        <f>B32</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="26" t="str">
-        <f>C32</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="26" t="str">
-        <f>D32</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="26" t="str">
-        <f>E32</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="26" t="str">
-        <f>F32</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B39" s="29">
-        <f>B36+B37+B38</f>
-        <v>94141</v>
-      </c>
-      <c r="C39" s="29">
-        <f>C36+C37+C38</f>
-        <v>120953</v>
-      </c>
-      <c r="D39" s="29">
-        <f>D36+D37+D38</f>
-        <v>129949</v>
-      </c>
-      <c r="E39" s="29">
-        <f>E36+E37+E38</f>
-        <v>137923</v>
-      </c>
-      <c r="F39" s="29">
-        <f>F36+F37+F38</f>
-        <v>144782</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-    </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" s="31">
-        <f>B35-B39</f>
-        <v>73359</v>
-      </c>
-      <c r="C41" s="31">
-        <f>C35-C39</f>
-        <v>179782</v>
-      </c>
-      <c r="D41" s="31">
-        <f>D35-D39</f>
-        <v>289250</v>
-      </c>
-      <c r="E41" s="31">
-        <f>E35-E39</f>
-        <v>377046</v>
-      </c>
-      <c r="F41" s="31">
-        <f>F35-F39</f>
-        <v>441343</v>
+      <c r="A41" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B41" s="27">
+        <f>B33</f>
+        <v>33375</v>
+      </c>
+      <c r="C41" s="27">
+        <f>C33</f>
+        <v>45711</v>
+      </c>
+      <c r="D41" s="27">
+        <f>D33</f>
+        <v>52315</v>
+      </c>
+      <c r="E41" s="27">
+        <f>E33</f>
+        <v>57825</v>
+      </c>
+      <c r="F41" s="27">
+        <f>F33</f>
+        <v>62146</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" s="32">
-        <f>IF(B35=0,"",B41/B35)</f>
-        <v>0.44</v>
-      </c>
-      <c r="C42" s="32">
-        <f>IF(C35=0,"",C41/C35)</f>
-        <v>0.6</v>
-      </c>
-      <c r="D42" s="32">
-        <f>IF(D35=0,"",D41/D35)</f>
-        <v>0.69</v>
-      </c>
-      <c r="E42" s="32">
-        <f>IF(E35=0,"",E41/E35)</f>
-        <v>0.73</v>
-      </c>
-      <c r="F42" s="32">
-        <f>IF(F35=0,"",F41/F35)</f>
-        <v>0.75</v>
+        <v>150</v>
+      </c>
+      <c r="B42" s="27" t="str">
+        <f>B36</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="27" t="str">
+        <f>C36</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="27" t="str">
+        <f>D36</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="27" t="str">
+        <f>E36</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="27" t="str">
+        <f>F36</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B43" s="26">
-        <f>B41</f>
-        <v>73359</v>
-      </c>
-      <c r="C43" s="26">
-        <f>B43+C41</f>
-        <v>253141</v>
-      </c>
-      <c r="D43" s="26">
-        <f>C43+D41</f>
-        <v>542391</v>
-      </c>
-      <c r="E43" s="26">
-        <f>D43+E41</f>
-        <v>919437</v>
-      </c>
-      <c r="F43" s="26">
-        <f>E43+F41</f>
-        <v>1360780</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="B44" s="33" t="s">
+      <c r="A43" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="B43" s="30">
+        <f>B40+B41+B42</f>
+        <v>97891</v>
+      </c>
+      <c r="C43" s="30">
+        <f>C40+C41+C42</f>
+        <v>125453</v>
+      </c>
+      <c r="D43" s="30">
+        <f>D40+D41+D42</f>
+        <v>134449</v>
+      </c>
+      <c r="E43" s="30">
+        <f>E40+E41+E42</f>
+        <v>142423</v>
+      </c>
+      <c r="F43" s="30">
+        <f>F40+F41+F42</f>
+        <v>149282</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>7</v>
       </c>
-      <c r="D44" s="34" t="s">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="32">
+        <f>B39-B43</f>
+        <v>69609</v>
+      </c>
+      <c r="C45" s="32">
+        <f>C39-C43</f>
+        <v>175172</v>
+      </c>
+      <c r="D45" s="32">
+        <f>D39-D43</f>
+        <v>284447</v>
+      </c>
+      <c r="E45" s="32">
+        <f>E39-E43</f>
+        <v>371992</v>
+      </c>
+      <c r="F45" s="32">
+        <f>F39-F43</f>
+        <v>436012</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="33">
+        <f>IF(B39=0,"",B45/B39)</f>
+        <v>0.41557612</v>
+      </c>
+      <c r="C46" s="33">
+        <f>IF(C39=0,"",C45/C39)</f>
+        <v>0.58269272</v>
+      </c>
+      <c r="D46" s="33">
+        <f>IF(D39=0,"",D45/D39)</f>
+        <v>0.67903967</v>
+      </c>
+      <c r="E46" s="33">
+        <f>IF(E39=0,"",E45/E39)</f>
+        <v>0.72313599</v>
+      </c>
+      <c r="F46" s="33">
+        <f>IF(F39=0,"",F45/F39)</f>
+        <v>0.74494528</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B47" s="27">
+        <f>B45</f>
+        <v>69609</v>
+      </c>
+      <c r="C47" s="27">
+        <f>B47+C45</f>
+        <v>244781</v>
+      </c>
+      <c r="D47" s="27">
+        <f>C47+D45</f>
+        <v>529228</v>
+      </c>
+      <c r="E47" s="27">
+        <f>D47+E45</f>
+        <v>901220</v>
+      </c>
+      <c r="F47" s="27">
+        <f>E47+F45</f>
+        <v>1337232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E44" s="34" t="s">
+      <c r="D48" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="34" t="s">
+      <c r="E48" s="35" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="B47" s="29">
-        <f>B35-B36-B37</f>
-        <v>73359</v>
-      </c>
-      <c r="C47" s="29">
-        <f>C35-C36-C37</f>
-        <v>179782</v>
-      </c>
-      <c r="D47" s="29">
-        <f>D35-D36-D37</f>
-        <v>289250</v>
-      </c>
-      <c r="E47" s="29">
-        <f>E35-E36-E37</f>
-        <v>377046</v>
-      </c>
-      <c r="F47" s="29">
-        <f>F35-F36-F37</f>
-        <v>441343</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B48" s="26" t="str">
-        <f>B38</f>
-        <v>0</v>
-      </c>
-      <c r="C48" s="26" t="str">
-        <f>C38</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="26" t="str">
-        <f>D38</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="26" t="str">
-        <f>E38</f>
-        <v>0</v>
-      </c>
-      <c r="F48" s="26" t="str">
-        <f>F38</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="B49" s="35" t="str">
-        <f>IF(B48=0,"N/A",B47/B48)</f>
-        <v>N/A</v>
-      </c>
-      <c r="C49" s="35" t="str">
-        <f>IF(C48=0,"N/A",C47/C48)</f>
-        <v>N/A</v>
-      </c>
-      <c r="D49" s="35" t="str">
-        <f>IF(D48=0,"N/A",D47/D48)</f>
-        <v>N/A</v>
-      </c>
-      <c r="E49" s="35" t="str">
-        <f>IF(E48=0,"N/A",E47/E48)</f>
-        <v>N/A</v>
-      </c>
-      <c r="F49" s="35" t="str">
-        <f>IF(F48=0,"N/A",F47/F48)</f>
-        <v>N/A</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B50" s="26" t="str">
-        <f>Assumptions!B50</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="26">
-        <f>B51</f>
-        <v>73359</v>
-      </c>
-      <c r="D50" s="26">
-        <f>C51</f>
-        <v>253141</v>
-      </c>
-      <c r="E50" s="26">
-        <f>D51</f>
-        <v>542391</v>
-      </c>
-      <c r="F50" s="26">
-        <f>E51</f>
-        <v>919437</v>
-      </c>
+      <c r="F48" s="35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51" s="29">
-        <f>B50+B41</f>
-        <v>73359</v>
-      </c>
-      <c r="C51" s="29">
-        <f>C50+C41</f>
-        <v>253141</v>
-      </c>
-      <c r="D51" s="29">
-        <f>D50+D41</f>
-        <v>542391</v>
-      </c>
-      <c r="E51" s="29">
-        <f>E50+E41</f>
-        <v>919437</v>
-      </c>
-      <c r="F51" s="29">
-        <f>F50+F41</f>
-        <v>1360780</v>
+      <c r="A51" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="30">
+        <f>B39-B40-B41</f>
+        <v>69609</v>
+      </c>
+      <c r="C51" s="30">
+        <f>C39-C40-C41</f>
+        <v>175172</v>
+      </c>
+      <c r="D51" s="30">
+        <f>D39-D40-D41</f>
+        <v>284447</v>
+      </c>
+      <c r="E51" s="30">
+        <f>E39-E40-E41</f>
+        <v>371992</v>
+      </c>
+      <c r="F51" s="30">
+        <f>F39-F40-F41</f>
+        <v>436012</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B52" s="36">
-        <f>IF(B39=0,"",B51/B39*365)</f>
-        <v>284</v>
-      </c>
-      <c r="C52" s="36">
-        <f>IF(C39=0,"",C51/C39*365)</f>
-        <v>764</v>
-      </c>
-      <c r="D52" s="36">
-        <f>IF(D39=0,"",D51/D39*365)</f>
-        <v>1523</v>
-      </c>
-      <c r="E52" s="36">
-        <f>IF(E39=0,"",E51/E39*365)</f>
-        <v>2433</v>
-      </c>
-      <c r="F52" s="36">
-        <f>IF(F39=0,"",F51/F39*365)</f>
-        <v>3431</v>
+        <v>159</v>
+      </c>
+      <c r="B52" s="27" t="str">
+        <f>B42</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="27" t="str">
+        <f>C42</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="27" t="str">
+        <f>D42</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="27" t="str">
+        <f>E42</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="27" t="str">
+        <f>F42</f>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B53" s="37">
-        <f>IF(B39=0,"",B51/(B39/12))</f>
-        <v>9.4</v>
-      </c>
-      <c r="C53" s="37">
-        <f>IF(C39=0,"",C51/(C39/12))</f>
-        <v>25.1</v>
-      </c>
-      <c r="D53" s="37">
-        <f>IF(D39=0,"",D51/(D39/12))</f>
-        <v>50.1</v>
-      </c>
-      <c r="E53" s="37">
-        <f>IF(E39=0,"",E51/(E39/12))</f>
-        <v>80</v>
-      </c>
-      <c r="F53" s="37">
-        <f>IF(F39=0,"",F51/(F39/12))</f>
-        <v>112.8</v>
+      <c r="A53" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B53" s="36" t="str">
+        <f>IF(B52=0,"N/A",B51/B52)</f>
+        <v>N/A</v>
+      </c>
+      <c r="C53" s="36" t="str">
+        <f>IF(C52=0,"N/A",C51/C52)</f>
+        <v>N/A</v>
+      </c>
+      <c r="D53" s="36" t="str">
+        <f>IF(D52=0,"N/A",D51/D52)</f>
+        <v>N/A</v>
+      </c>
+      <c r="E53" s="36" t="str">
+        <f>IF(E52=0,"N/A",E51/E52)</f>
+        <v>N/A</v>
+      </c>
+      <c r="F53" s="36" t="str">
+        <f>IF(F52=0,"N/A",F51/F52)</f>
+        <v>N/A</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="32">
-        <f>IF(Assumptions!B12=0,"",B3/Assumptions!B12)</f>
-        <v>0.38</v>
-      </c>
-      <c r="C54" s="32">
-        <f>IF(Assumptions!B12=0,"",C3/Assumptions!B12)</f>
-        <v>0.55</v>
-      </c>
-      <c r="D54" s="32">
-        <f>IF(Assumptions!B12=0,"",D3/Assumptions!B12)</f>
-        <v>0.75</v>
-      </c>
-      <c r="E54" s="32">
-        <f>IF(Assumptions!B12=0,"",E3/Assumptions!B12)</f>
-        <v>0.9</v>
-      </c>
-      <c r="F54" s="32">
-        <f>IF(Assumptions!B12=0,"",F3/Assumptions!B12)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
+        <v>123</v>
+      </c>
+      <c r="B54" s="27" t="str">
+        <f>Assumptions!B51</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="27">
+        <f>B55</f>
+        <v>69609</v>
+      </c>
+      <c r="D54" s="27">
+        <f>C55</f>
+        <v>244781</v>
+      </c>
+      <c r="E54" s="27">
+        <f>D55</f>
+        <v>529228</v>
+      </c>
+      <c r="F54" s="27">
+        <f>E55</f>
+        <v>901220</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="30">
+        <f>B54+B45</f>
+        <v>69609</v>
+      </c>
+      <c r="C55" s="30">
+        <f>C54+C45</f>
+        <v>244781</v>
+      </c>
+      <c r="D55" s="30">
+        <f>D54+D45</f>
+        <v>529228</v>
+      </c>
+      <c r="E55" s="30">
+        <f>E54+E45</f>
+        <v>901220</v>
+      </c>
+      <c r="F55" s="30">
+        <f>F54+F45</f>
+        <v>1337232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="37">
+        <f>IF(B43=0,"",B55/B43*365)</f>
+        <v>260</v>
+      </c>
+      <c r="C56" s="37">
+        <f>IF(C43=0,"",C55/C43*365)</f>
+        <v>712</v>
+      </c>
+      <c r="D56" s="37">
+        <f>IF(D43=0,"",D55/D43*365)</f>
+        <v>1437</v>
+      </c>
+      <c r="E56" s="37">
+        <f>IF(E43=0,"",E55/E43*365)</f>
+        <v>2310</v>
+      </c>
+      <c r="F56" s="37">
+        <f>IF(F43=0,"",F55/F43*365)</f>
+        <v>3270</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B57" s="13" t="str">
-        <f>IF(B48=0,"N/A",IF(B49&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="C57" s="13" t="str">
-        <f>IF(C48=0,"N/A",IF(C49&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="D57" s="13" t="str">
-        <f>IF(D48=0,"N/A",IF(D49&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="E57" s="13" t="str">
-        <f>IF(E48=0,"N/A",IF(E49&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
-      </c>
-      <c r="F57" s="13" t="str">
-        <f>IF(F48=0,"N/A",IF(F49&gt;=1.2,"PASS","FAIL"))</f>
-        <v>N/A</v>
+        <v>163</v>
+      </c>
+      <c r="B57" s="38">
+        <f>IF(B43=0,"",B55/(B43/12))</f>
+        <v>8.5</v>
+      </c>
+      <c r="C57" s="38">
+        <f>IF(C43=0,"",C55/(C43/12))</f>
+        <v>23.4</v>
+      </c>
+      <c r="D57" s="38">
+        <f>IF(D43=0,"",D55/(D43/12))</f>
+        <v>47.2</v>
+      </c>
+      <c r="E57" s="38">
+        <f>IF(E43=0,"",E55/(E43/12))</f>
+        <v>75.9</v>
+      </c>
+      <c r="F57" s="38">
+        <f>IF(F43=0,"",F55/(F43/12))</f>
+        <v>107.5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="13" t="str">
-        <f>IF(B41&gt;0,"PASS","FAIL")</f>
+        <v>164</v>
+      </c>
+      <c r="B58" s="33">
+        <f>IF(Assumptions!B12=0,"",B4/Assumptions!B12)</f>
+        <v>0.375</v>
+      </c>
+      <c r="C58" s="33">
+        <f>IF(Assumptions!B12=0,"",C4/Assumptions!B12)</f>
+        <v>0.55</v>
+      </c>
+      <c r="D58" s="33">
+        <f>IF(Assumptions!B12=0,"",D4/Assumptions!B12)</f>
+        <v>0.75</v>
+      </c>
+      <c r="E58" s="33">
+        <f>IF(Assumptions!B12=0,"",E4/Assumptions!B12)</f>
+        <v>0.9</v>
+      </c>
+      <c r="F58" s="33">
+        <f>IF(Assumptions!B12=0,"",F4/Assumptions!B12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B61" s="13" t="str">
+        <f>IF(B52=0,"N/A",IF(B53&gt;=1.25,"PASS","FAIL"))</f>
+        <v>N/A</v>
+      </c>
+      <c r="C61" s="13" t="str">
+        <f>IF(C52=0,"N/A",IF(C53&gt;=1.25,"PASS","FAIL"))</f>
+        <v>N/A</v>
+      </c>
+      <c r="D61" s="13" t="str">
+        <f>IF(D52=0,"N/A",IF(D53&gt;=1.25,"PASS","FAIL"))</f>
+        <v>N/A</v>
+      </c>
+      <c r="E61" s="13" t="str">
+        <f>IF(E52=0,"N/A",IF(E53&gt;=1.25,"PASS","FAIL"))</f>
+        <v>N/A</v>
+      </c>
+      <c r="F61" s="13" t="str">
+        <f>IF(F52=0,"N/A",IF(F53&gt;=1.25,"PASS","FAIL"))</f>
+        <v>N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B62" s="13" t="str">
+        <f>IF(B45&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="C58" s="13" t="str">
-        <f>IF(C41&gt;0,"PASS","FAIL")</f>
+      <c r="C62" s="13" t="str">
+        <f>IF(C45&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="D58" s="13" t="str">
-        <f>IF(D41&gt;0,"PASS","FAIL")</f>
+      <c r="D62" s="13" t="str">
+        <f>IF(D45&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="E58" s="13" t="str">
-        <f>IF(E41&gt;0,"PASS","FAIL")</f>
+      <c r="E62" s="13" t="str">
+        <f>IF(E45&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-      <c r="F58" s="13" t="str">
-        <f>IF(F41&gt;0,"PASS","FAIL")</f>
+      <c r="F62" s="13" t="str">
+        <f>IF(F45&gt;0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B59" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(B3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="C59" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(C3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>FAIL</v>
-      </c>
-      <c r="D59" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(D3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E59" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(E3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F59" s="13" t="str">
-        <f>IF(Assumptions!B12=0,"N/A",IF(F3/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B60" s="13" t="str">
-        <f>IF(B39=0,"N/A",IF(B51/(B39/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="C60" s="13" t="str">
-        <f>IF(C39=0,"N/A",IF(C51/(C39/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="D60" s="13" t="str">
-        <f>IF(D39=0,"N/A",IF(D51/(D39/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="E60" s="13" t="str">
-        <f>IF(E39=0,"N/A",IF(E51/(E39/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-      <c r="F60" s="13" t="str">
-        <f>IF(F39=0,"N/A",IF(F51/(F39/12)&gt;=2,"PASS","FAIL"))</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B63" s="26">
-        <f>IF(B3=0,"",B10/B3)</f>
-        <v>11167</v>
-      </c>
-      <c r="C63" s="26">
-        <f>IF(C3=0,"",C10/C3)</f>
-        <v>13670</v>
-      </c>
-      <c r="D63" s="26">
-        <f>IF(D3=0,"",D10/D3)</f>
-        <v>13973</v>
-      </c>
-      <c r="E63" s="26">
-        <f>IF(E3=0,"",E10/E3)</f>
-        <v>14305</v>
-      </c>
-      <c r="F63" s="26">
-        <f>IF(F3=0,"",F10/F3)</f>
-        <v>14653</v>
+        <v>168</v>
+      </c>
+      <c r="B63" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(B4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="C63" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(C4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="D63" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(D4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E63" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(E4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F63" s="13" t="str">
+        <f>IF(Assumptions!B12=0,"N/A",IF(F4/Assumptions!B12&gt;=0.7,"PASS","FAIL"))</f>
+        <v>PASS</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="B64" s="26">
-        <f>IF(B3=0,"",B39/B3)</f>
-        <v>6276</v>
-      </c>
-      <c r="C64" s="26">
-        <f>IF(C3=0,"",C39/C3)</f>
-        <v>5498</v>
-      </c>
-      <c r="D64" s="26">
-        <f>IF(D3=0,"",D39/D3)</f>
-        <v>4332</v>
-      </c>
-      <c r="E64" s="26">
-        <f>IF(E3=0,"",E39/E3)</f>
-        <v>3831</v>
-      </c>
-      <c r="F64" s="26">
-        <f>IF(F3=0,"",F39/F3)</f>
-        <v>3620</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B65" s="26">
-        <f>B36+B38</f>
-        <v>64516</v>
-      </c>
-      <c r="C65" s="26">
-        <f>C36+C38</f>
-        <v>79742</v>
-      </c>
-      <c r="D65" s="26">
-        <f>D36+D38</f>
-        <v>82134</v>
-      </c>
-      <c r="E65" s="26">
-        <f>E36+E38</f>
-        <v>84598</v>
-      </c>
-      <c r="F65" s="26">
-        <f>F36+F38</f>
-        <v>87136</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="B66" s="26">
-        <f>IF(B3=0,"",B37/B3)</f>
-        <v>1975</v>
-      </c>
-      <c r="C66" s="26">
-        <f>IF(C3=0,"",C37/C3)</f>
-        <v>1873</v>
-      </c>
-      <c r="D66" s="26">
-        <f>IF(D3=0,"",D37/D3)</f>
-        <v>1594</v>
-      </c>
-      <c r="E66" s="26">
-        <f>IF(E3=0,"",E37/E3)</f>
-        <v>1481</v>
-      </c>
-      <c r="F66" s="26">
-        <f>IF(F3=0,"",F37/F3)</f>
-        <v>1441</v>
-      </c>
+      <c r="B64" s="13" t="str">
+        <f>IF(B43=0,"N/A",IF(B55/(B43/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="C64" s="13" t="str">
+        <f>IF(C43=0,"N/A",IF(C55/(C43/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="D64" s="13" t="str">
+        <f>IF(D43=0,"N/A",IF(D55/(D43/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="E64" s="13" t="str">
+        <f>IF(E43=0,"N/A",IF(E55/(E43/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+      <c r="F64" s="13" t="str">
+        <f>IF(F43=0,"N/A",IF(F55/(F43/12)&gt;=2,"PASS","FAIL"))</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B67" s="26">
-        <f>IF(B3=0,"",B63-B66)</f>
-        <v>9192</v>
-      </c>
-      <c r="C67" s="26">
-        <f>IF(C3=0,"",C63-C66)</f>
-        <v>11797</v>
-      </c>
-      <c r="D67" s="26">
-        <f>IF(D3=0,"",D63-D66)</f>
-        <v>12379</v>
-      </c>
-      <c r="E67" s="26">
-        <f>IF(E3=0,"",E63-E66)</f>
-        <v>12823</v>
-      </c>
-      <c r="F67" s="26">
-        <f>IF(F3=0,"",F63-F66)</f>
-        <v>13212</v>
+        <v>171</v>
+      </c>
+      <c r="B67" s="27">
+        <f>IF(B4=0,"",B11/B4)</f>
+        <v>11167</v>
+      </c>
+      <c r="C67" s="27">
+        <f>IF(C4=0,"",C11/C4)</f>
+        <v>13665</v>
+      </c>
+      <c r="D67" s="27">
+        <f>IF(D4=0,"",D11/D4)</f>
+        <v>13963</v>
+      </c>
+      <c r="E67" s="27">
+        <f>IF(E4=0,"",E11/E4)</f>
+        <v>14289</v>
+      </c>
+      <c r="F67" s="27">
+        <f>IF(F4=0,"",F11/F4)</f>
+        <v>14632</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="B68" s="39">
-        <f>IF(B67&lt;=0,"N/A",ROUNDUP(B65/B67,0))</f>
+      <c r="A68" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B68" s="27">
+        <f>IF(B4=0,"",B43/B4)</f>
+        <v>6526</v>
+      </c>
+      <c r="C68" s="27">
+        <f>IF(C4=0,"",C43/C4)</f>
+        <v>5702</v>
+      </c>
+      <c r="D68" s="27">
+        <f>IF(D4=0,"",D43/D4)</f>
+        <v>4482</v>
+      </c>
+      <c r="E68" s="27">
+        <f>IF(E4=0,"",E43/E4)</f>
+        <v>3956</v>
+      </c>
+      <c r="F68" s="27">
+        <f>IF(F4=0,"",F43/F4)</f>
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B69" s="27">
+        <f>B40+B42</f>
+        <v>64516</v>
+      </c>
+      <c r="C69" s="27">
+        <f>C40+C42</f>
+        <v>79742</v>
+      </c>
+      <c r="D69" s="27">
+        <f>D40+D42</f>
+        <v>82134</v>
+      </c>
+      <c r="E69" s="27">
+        <f>E40+E42</f>
+        <v>84598</v>
+      </c>
+      <c r="F69" s="27">
+        <f>F40+F42</f>
+        <v>87136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" s="27">
+        <f>IF(B4=0,"",B41/B4)</f>
+        <v>2225</v>
+      </c>
+      <c r="C70" s="27">
+        <f>IF(C4=0,"",C41/C4)</f>
+        <v>2078</v>
+      </c>
+      <c r="D70" s="27">
+        <f>IF(D4=0,"",D41/D4)</f>
+        <v>1744</v>
+      </c>
+      <c r="E70" s="27">
+        <f>IF(E4=0,"",E41/E4)</f>
+        <v>1606</v>
+      </c>
+      <c r="F70" s="27">
+        <f>IF(F4=0,"",F41/F4)</f>
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B71" s="27">
+        <f>IF(B4=0,"",B67-B70)</f>
+        <v>8942</v>
+      </c>
+      <c r="C71" s="27">
+        <f>IF(C4=0,"",C67-C70)</f>
+        <v>11587</v>
+      </c>
+      <c r="D71" s="27">
+        <f>IF(D4=0,"",D67-D70)</f>
+        <v>12219</v>
+      </c>
+      <c r="E71" s="27">
+        <f>IF(E4=0,"",E67-E70)</f>
+        <v>12683</v>
+      </c>
+      <c r="F71" s="27">
+        <f>IF(F4=0,"",F67-F70)</f>
+        <v>13079</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="B72" s="40">
+        <f>IF(B71&lt;=0,"N/A",ROUNDUP(B69/B71,0))</f>
         <v>8</v>
       </c>
-      <c r="C68" s="39">
-        <f>IF(C67&lt;=0,"N/A",ROUNDUP(C65/C67,0))</f>
+      <c r="C72" s="40">
+        <f>IF(C71&lt;=0,"N/A",ROUNDUP(C69/C71,0))</f>
         <v>7</v>
       </c>
-      <c r="D68" s="39">
-        <f>IF(D67&lt;=0,"N/A",ROUNDUP(D65/D67,0))</f>
+      <c r="D72" s="40">
+        <f>IF(D71&lt;=0,"N/A",ROUNDUP(D69/D71,0))</f>
         <v>7</v>
       </c>
-      <c r="E68" s="39">
-        <f>IF(E67&lt;=0,"N/A",ROUNDUP(E65/E67,0))</f>
+      <c r="E72" s="40">
+        <f>IF(E71&lt;=0,"N/A",ROUNDUP(E69/E71,0))</f>
         <v>7</v>
       </c>
-      <c r="F68" s="39">
-        <f>IF(F67&lt;=0,"N/A",ROUNDUP(F65/F67,0))</f>
+      <c r="F72" s="40">
+        <f>IF(F71&lt;=0,"N/A",ROUNDUP(F69/F71,0))</f>
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B70" s="22"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A74:F74"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -3726,7 +3832,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -3736,7 +3842,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3753,52 +3859,52 @@
       <c r="N1" s="8"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="H2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="D2" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="F2" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="L2" s="23" t="s">
+      <c r="G2" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="H2" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="N2" s="23" t="s">
+      <c r="I2" s="24" t="s">
         <v>184</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="M2" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="N2" s="24" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -3818,43 +3924,43 @@
       <c r="A4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="27">
         <v>9000</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>9000</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>9000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>9000</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <v>9000</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="27">
         <v>9000</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="27">
         <v>9000</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="27">
         <v>9000</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="27">
         <v>9000</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="27">
         <v>9000</v>
       </c>
-      <c r="L4" s="26">
-        <v>0</v>
-      </c>
-      <c r="M4" s="26">
-        <v>0</v>
-      </c>
-      <c r="N4" s="26">
+      <c r="L4" s="27">
+        <v>0</v>
+      </c>
+      <c r="M4" s="27">
+        <v>0</v>
+      </c>
+      <c r="N4" s="27">
         <f>SUM(B4:M4)</f>
         <v>75000</v>
       </c>
@@ -3863,43 +3969,43 @@
       <c r="A5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="27">
         <v>300</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>300</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <v>300</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>300</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <v>300</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="27">
         <v>300</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="27">
         <v>300</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="27">
         <v>300</v>
       </c>
-      <c r="J5" s="26">
+      <c r="J5" s="27">
         <v>300</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="27">
         <v>300</v>
       </c>
-      <c r="L5" s="26">
-        <v>0</v>
-      </c>
-      <c r="M5" s="26">
-        <v>0</v>
-      </c>
-      <c r="N5" s="26">
+      <c r="L5" s="27">
+        <v>0</v>
+      </c>
+      <c r="M5" s="27">
+        <v>0</v>
+      </c>
+      <c r="N5" s="27">
         <f>SUM(B5:M5)</f>
         <v>2500</v>
       </c>
@@ -3908,43 +4014,43 @@
       <c r="A6" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>10500</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>10500</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>10500</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>10500</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <v>10500</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <v>10500</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <v>10500</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <v>10500</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="27">
         <v>10500</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="27">
         <v>10500</v>
       </c>
-      <c r="L6" s="26">
-        <v>0</v>
-      </c>
-      <c r="M6" s="26">
-        <v>0</v>
-      </c>
-      <c r="N6" s="26">
+      <c r="L6" s="27">
+        <v>0</v>
+      </c>
+      <c r="M6" s="27">
+        <v>0</v>
+      </c>
+      <c r="N6" s="27">
         <f>SUM(B6:M6)</f>
         <v>87500</v>
       </c>
@@ -3953,100 +4059,100 @@
       <c r="A7" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="27">
         <v>300</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <v>300</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <v>300</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>300</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <v>300</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="27">
         <v>300</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="27">
         <v>300</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <v>300</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="27">
         <v>300</v>
       </c>
-      <c r="K7" s="26">
+      <c r="K7" s="27">
         <v>300</v>
       </c>
-      <c r="L7" s="26">
-        <v>0</v>
-      </c>
-      <c r="M7" s="26">
-        <v>0</v>
-      </c>
-      <c r="N7" s="26">
+      <c r="L7" s="27">
+        <v>0</v>
+      </c>
+      <c r="M7" s="27">
+        <v>0</v>
+      </c>
+      <c r="N7" s="27">
         <f>SUM(B7:M7)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="27">
+        <v>128</v>
+      </c>
+      <c r="B8" s="28">
         <f>SUM(B4:B7)</f>
         <v>103800</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>SUM(C4:C7)</f>
         <v>10800</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>SUM(D4:D7)</f>
         <v>10800</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>SUM(E4:E7)</f>
         <v>10800</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f>SUM(F4:F7)</f>
         <v>10800</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <f>SUM(G4:G7)</f>
         <v>10800</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="28">
         <f>SUM(H4:H7)</f>
         <v>10800</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="28">
         <f>SUM(I4:I7)</f>
         <v>10800</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="28">
         <f>SUM(J4:J7)</f>
         <v>10800</v>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="28">
         <f>SUM(K4:K7)</f>
         <v>10800</v>
       </c>
-      <c r="L8" s="27" t="str">
+      <c r="L8" s="28" t="str">
         <f>SUM(L4:L7)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="27" t="str">
+      <c r="M8" s="28" t="str">
         <f>SUM(M4:M7)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="28">
         <f>SUM(B8:M8)</f>
         <v>201000</v>
       </c>
@@ -4058,7 +4164,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -4078,43 +4184,43 @@
       <c r="A11" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <v>5106</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>5106</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <v>5106</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>5106</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <v>5106</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <v>5106</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="27">
         <v>5106</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="27">
         <v>5106</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="27">
         <v>5106</v>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="27">
         <v>5106</v>
       </c>
-      <c r="L11" s="26">
-        <v>0</v>
-      </c>
-      <c r="M11" s="26">
-        <v>0</v>
-      </c>
-      <c r="N11" s="26">
+      <c r="L11" s="27">
+        <v>0</v>
+      </c>
+      <c r="M11" s="27">
+        <v>0</v>
+      </c>
+      <c r="N11" s="27">
         <f>SUM(B11:M11)</f>
         <v>51060</v>
       </c>
@@ -4123,100 +4229,100 @@
       <c r="A12" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <v>1346</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>1346</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>1346</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>1346</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <v>1346</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <v>1346</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <v>1346</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <v>1346</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="27">
         <v>1346</v>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="27">
         <v>1346</v>
       </c>
-      <c r="L12" s="26">
-        <v>0</v>
-      </c>
-      <c r="M12" s="26">
-        <v>0</v>
-      </c>
-      <c r="N12" s="26">
+      <c r="L12" s="27">
+        <v>0</v>
+      </c>
+      <c r="M12" s="27">
+        <v>0</v>
+      </c>
+      <c r="N12" s="27">
         <f>SUM(B12:M12)</f>
         <v>13456</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="27">
+        <v>132</v>
+      </c>
+      <c r="B13" s="28">
         <f>SUM(B11:B12)</f>
         <v>6452</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>SUM(C11:C12)</f>
         <v>6452</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>SUM(D11:D12)</f>
         <v>6452</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="28">
         <f>SUM(E11:E12)</f>
         <v>6452</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <f>SUM(F11:F12)</f>
         <v>6452</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <f>SUM(G11:G12)</f>
         <v>6452</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="28">
         <f>SUM(H11:H12)</f>
         <v>6452</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="28">
         <f>SUM(I11:I12)</f>
         <v>6452</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="28">
         <f>SUM(J11:J12)</f>
         <v>6452</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="28">
         <f>SUM(K11:K12)</f>
         <v>6452</v>
       </c>
-      <c r="L13" s="27" t="str">
+      <c r="L13" s="28" t="str">
         <f>SUM(L11:L12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="27" t="str">
+      <c r="M13" s="28" t="str">
         <f>SUM(M11:M12)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="28">
         <f>SUM(B13:M13)</f>
         <v>64516</v>
       </c>
@@ -4246,7 +4352,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4264,97 +4370,97 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="B17" s="26">
+        <v>190</v>
+      </c>
+      <c r="B17" s="27">
         <v>500</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>500</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>500</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>500</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>500</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="27">
         <v>500</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="27">
         <v>500</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <v>500</v>
       </c>
-      <c r="J17" s="26">
+      <c r="J17" s="27">
         <v>500</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="27">
         <v>500</v>
       </c>
-      <c r="L17" s="26">
-        <v>0</v>
-      </c>
-      <c r="M17" s="26">
-        <v>0</v>
-      </c>
-      <c r="N17" s="26">
+      <c r="L17" s="27">
+        <v>0</v>
+      </c>
+      <c r="M17" s="27">
+        <v>0</v>
+      </c>
+      <c r="N17" s="27">
         <f>SUM(B17:M17)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="A18" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="30">
         <v>500</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>500</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>500</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <v>500</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <v>500</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <v>500</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="30">
         <v>500</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="30">
         <v>500</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="30">
         <v>500</v>
       </c>
-      <c r="K18" s="29">
+      <c r="K18" s="30">
         <v>500</v>
       </c>
-      <c r="L18" s="29">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29">
-        <v>0</v>
-      </c>
-      <c r="N18" s="29">
+      <c r="L18" s="30">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30">
+        <v>0</v>
+      </c>
+      <c r="N18" s="30">
         <f>SUM(B18:M18)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -4372,90 +4478,90 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B20" s="26">
+        <v>191</v>
+      </c>
+      <c r="B20" s="27">
         <v>313</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <v>313</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <v>313</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <v>313</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <v>313</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <v>313</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="27">
         <v>313</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <v>313</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="27">
         <v>313</v>
       </c>
-      <c r="K20" s="26">
+      <c r="K20" s="27">
         <v>313</v>
       </c>
-      <c r="L20" s="26">
-        <v>0</v>
-      </c>
-      <c r="M20" s="26">
-        <v>0</v>
-      </c>
-      <c r="N20" s="26">
+      <c r="L20" s="27">
+        <v>0</v>
+      </c>
+      <c r="M20" s="27">
+        <v>0</v>
+      </c>
+      <c r="N20" s="27">
         <f>SUM(B20:M20)</f>
         <v>3125</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="30">
         <v>313</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>313</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>313</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>313</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>313</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>313</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>313</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>313</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>313</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>313</v>
       </c>
-      <c r="L21" s="29">
-        <v>0</v>
-      </c>
-      <c r="M21" s="29">
-        <v>0</v>
-      </c>
-      <c r="N21" s="29">
+      <c r="L21" s="30">
+        <v>0</v>
+      </c>
+      <c r="M21" s="30">
+        <v>0</v>
+      </c>
+      <c r="N21" s="30">
         <f>SUM(B21:M21)</f>
         <v>3125</v>
       </c>
@@ -4480,540 +4586,648 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B23" s="26">
+        <v>192</v>
+      </c>
+      <c r="B23" s="27">
         <v>1800</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <v>1800</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <v>1800</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <v>1800</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="27">
         <v>1800</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="27">
         <v>1800</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="27">
         <v>1800</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="27">
         <v>1800</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23" s="27">
         <v>1800</v>
       </c>
-      <c r="K23" s="26">
+      <c r="K23" s="27">
         <v>1800</v>
       </c>
-      <c r="L23" s="26">
-        <v>0</v>
-      </c>
-      <c r="M23" s="26">
-        <v>0</v>
-      </c>
-      <c r="N23" s="26">
+      <c r="L23" s="27">
+        <v>0</v>
+      </c>
+      <c r="M23" s="27">
+        <v>0</v>
+      </c>
+      <c r="N23" s="27">
         <f>SUM(B23:M23)</f>
         <v>18000</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="26">
+        <v>193</v>
+      </c>
+      <c r="B24" s="27">
         <v>200</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>200</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <v>200</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>200</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <v>200</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="27">
         <v>200</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="27">
         <v>200</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="27">
         <v>200</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="27">
         <v>200</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="27">
         <v>200</v>
       </c>
-      <c r="L24" s="26">
-        <v>0</v>
-      </c>
-      <c r="M24" s="26">
-        <v>0</v>
-      </c>
-      <c r="N24" s="26">
+      <c r="L24" s="27">
+        <v>0</v>
+      </c>
+      <c r="M24" s="27">
+        <v>0</v>
+      </c>
+      <c r="N24" s="27">
         <f>SUM(B24:M24)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="B25" s="26">
+        <v>194</v>
+      </c>
+      <c r="B25" s="27">
         <v>150</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <v>150</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <v>150</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <v>150</v>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <v>150</v>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="27">
         <v>150</v>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="27">
         <v>150</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="27">
         <v>150</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="27">
         <v>150</v>
       </c>
-      <c r="K25" s="26">
+      <c r="K25" s="27">
         <v>150</v>
       </c>
-      <c r="L25" s="26">
-        <v>0</v>
-      </c>
-      <c r="M25" s="26">
-        <v>0</v>
-      </c>
-      <c r="N25" s="26">
+      <c r="L25" s="27">
+        <v>0</v>
+      </c>
+      <c r="M25" s="27">
+        <v>0</v>
+      </c>
+      <c r="N25" s="27">
         <f>SUM(B25:M25)</f>
         <v>1500</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="29">
+      <c r="A26" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="30">
         <v>2150</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>2150</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>2150</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <v>2150</v>
       </c>
-      <c r="F26" s="29">
+      <c r="F26" s="30">
         <v>2150</v>
       </c>
-      <c r="G26" s="29">
+      <c r="G26" s="30">
         <v>2150</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="30">
         <v>2150</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="30">
         <v>2150</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="30">
         <v>2150</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="30">
         <v>2150</v>
       </c>
-      <c r="L26" s="29">
-        <v>0</v>
-      </c>
-      <c r="M26" s="29">
-        <v>0</v>
-      </c>
-      <c r="N26" s="29">
+      <c r="L26" s="30">
+        <v>0</v>
+      </c>
+      <c r="M26" s="30">
+        <v>0</v>
+      </c>
+      <c r="N26" s="30">
         <f>SUM(B26:M26)</f>
         <v>21500</v>
       </c>
     </row>
-    <row r="27" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27" s="27">
-        <f>B18+B21+B26</f>
-        <v>2963</v>
-      </c>
-      <c r="C27" s="27">
-        <f>C18+C21+C26</f>
-        <v>2963</v>
-      </c>
-      <c r="D27" s="27">
-        <f>D18+D21+D26</f>
-        <v>2963</v>
-      </c>
-      <c r="E27" s="27">
-        <f>E18+E21+E26</f>
-        <v>2963</v>
-      </c>
-      <c r="F27" s="27">
-        <f>F18+F21+F26</f>
-        <v>2963</v>
-      </c>
-      <c r="G27" s="27">
-        <f>G18+G21+G26</f>
-        <v>2963</v>
-      </c>
-      <c r="H27" s="27">
-        <f>H18+H21+H26</f>
-        <v>2963</v>
-      </c>
-      <c r="I27" s="27">
-        <f>I18+I21+I26</f>
-        <v>2963</v>
-      </c>
-      <c r="J27" s="27">
-        <f>J18+J21+J26</f>
-        <v>2963</v>
-      </c>
-      <c r="K27" s="27">
-        <f>K18+K21+K26</f>
-        <v>2963</v>
-      </c>
-      <c r="L27" s="27" t="str">
-        <f>L18+L21+L26</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="27" t="str">
-        <f>M18+M21+M26</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="27">
-        <f>SUM(B27:M27)</f>
-        <v>29625</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="27">
+        <v>375</v>
+      </c>
+      <c r="C28" s="27">
+        <v>375</v>
+      </c>
+      <c r="D28" s="27">
+        <v>375</v>
+      </c>
+      <c r="E28" s="27">
+        <v>375</v>
+      </c>
+      <c r="F28" s="27">
+        <v>375</v>
+      </c>
+      <c r="G28" s="27">
+        <v>375</v>
+      </c>
+      <c r="H28" s="27">
+        <v>375</v>
+      </c>
+      <c r="I28" s="27">
+        <v>375</v>
+      </c>
+      <c r="J28" s="27">
+        <v>375</v>
+      </c>
+      <c r="K28" s="27">
+        <v>375</v>
+      </c>
+      <c r="L28" s="27">
+        <v>0</v>
+      </c>
+      <c r="M28" s="27">
+        <v>0</v>
+      </c>
+      <c r="N28" s="27">
+        <f>SUM(B28:M28)</f>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="30">
+        <v>375</v>
+      </c>
+      <c r="C29" s="30">
+        <v>375</v>
+      </c>
+      <c r="D29" s="30">
+        <v>375</v>
+      </c>
+      <c r="E29" s="30">
+        <v>375</v>
+      </c>
+      <c r="F29" s="30">
+        <v>375</v>
+      </c>
+      <c r="G29" s="30">
+        <v>375</v>
+      </c>
+      <c r="H29" s="30">
+        <v>375</v>
+      </c>
+      <c r="I29" s="30">
+        <v>375</v>
+      </c>
+      <c r="J29" s="30">
+        <v>375</v>
+      </c>
+      <c r="K29" s="30">
+        <v>375</v>
+      </c>
+      <c r="L29" s="30">
+        <v>0</v>
+      </c>
+      <c r="M29" s="30">
+        <v>0</v>
+      </c>
+      <c r="N29" s="30">
+        <f>SUM(B29:M29)</f>
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="28">
+        <f>B18+B21+B26+B29</f>
+        <v>3338</v>
+      </c>
+      <c r="C30" s="28">
+        <f>C18+C21+C26+C29</f>
+        <v>3338</v>
+      </c>
+      <c r="D30" s="28">
+        <f>D18+D21+D26+D29</f>
+        <v>3338</v>
+      </c>
+      <c r="E30" s="28">
+        <f>E18+E21+E26+E29</f>
+        <v>3338</v>
+      </c>
+      <c r="F30" s="28">
+        <f>F18+F21+F26+F29</f>
+        <v>3338</v>
+      </c>
+      <c r="G30" s="28">
+        <f>G18+G21+G26+G29</f>
+        <v>3338</v>
+      </c>
+      <c r="H30" s="28">
+        <f>H18+H21+H26+H29</f>
+        <v>3338</v>
+      </c>
+      <c r="I30" s="28">
+        <f>I18+I21+I26+I29</f>
+        <v>3338</v>
+      </c>
+      <c r="J30" s="28">
+        <f>J18+J21+J26+J29</f>
+        <v>3338</v>
+      </c>
+      <c r="K30" s="28">
+        <f>K18+K21+K26+K29</f>
+        <v>3338</v>
+      </c>
+      <c r="L30" s="28" t="str">
+        <f>L18+L21+L26+L29</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="28" t="str">
+        <f>M18+M21+M26+M29</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="28">
+        <f>SUM(B30:M30)</f>
+        <v>33375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="B29" s="26">
-        <v>0</v>
-      </c>
-      <c r="C29" s="26">
-        <v>0</v>
-      </c>
-      <c r="D29" s="26">
-        <v>0</v>
-      </c>
-      <c r="E29" s="26">
-        <v>0</v>
-      </c>
-      <c r="F29" s="26">
-        <v>0</v>
-      </c>
-      <c r="G29" s="26">
-        <v>0</v>
-      </c>
-      <c r="H29" s="26">
-        <v>0</v>
-      </c>
-      <c r="I29" s="26">
-        <v>0</v>
-      </c>
-      <c r="J29" s="26">
-        <v>0</v>
-      </c>
-      <c r="K29" s="26">
-        <v>0</v>
-      </c>
-      <c r="L29" s="26">
-        <v>0</v>
-      </c>
-      <c r="M29" s="26">
-        <v>0</v>
-      </c>
-      <c r="N29" s="26" t="str">
-        <f>SUM(B29:M29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="B32" s="27">
+        <v>0</v>
+      </c>
+      <c r="C32" s="27">
+        <v>0</v>
+      </c>
+      <c r="D32" s="27">
+        <v>0</v>
+      </c>
+      <c r="E32" s="27">
+        <v>0</v>
+      </c>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
+      <c r="G32" s="27">
+        <v>0</v>
+      </c>
+      <c r="H32" s="27">
+        <v>0</v>
+      </c>
+      <c r="I32" s="27">
+        <v>0</v>
+      </c>
+      <c r="J32" s="27">
+        <v>0</v>
+      </c>
+      <c r="K32" s="27">
+        <v>0</v>
+      </c>
+      <c r="L32" s="27">
+        <v>0</v>
+      </c>
+      <c r="M32" s="27">
+        <v>0</v>
+      </c>
+      <c r="N32" s="27" t="str">
+        <f>SUM(B32:M32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" s="29">
-        <f>B13+B27+B29</f>
-        <v>9415</v>
-      </c>
-      <c r="C32" s="29">
-        <f>C13+C27+C29</f>
-        <v>9415</v>
-      </c>
-      <c r="D32" s="29">
-        <f>D13+D27+D29</f>
-        <v>9415</v>
-      </c>
-      <c r="E32" s="29">
-        <f>E13+E27+E29</f>
-        <v>9415</v>
-      </c>
-      <c r="F32" s="29">
-        <f>F13+F27+F29</f>
-        <v>9415</v>
-      </c>
-      <c r="G32" s="29">
-        <f>G13+G27+G29</f>
-        <v>9415</v>
-      </c>
-      <c r="H32" s="29">
-        <f>H13+H27+H29</f>
-        <v>9415</v>
-      </c>
-      <c r="I32" s="29">
-        <f>I13+I27+I29</f>
-        <v>9415</v>
-      </c>
-      <c r="J32" s="29">
-        <f>J13+J27+J29</f>
-        <v>9415</v>
-      </c>
-      <c r="K32" s="29">
-        <f>K13+K27+K29</f>
-        <v>9415</v>
-      </c>
-      <c r="L32" s="29" t="str">
-        <f>L13+L27+L29</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="29" t="str">
-        <f>M13+M27+M29</f>
-        <v>0</v>
-      </c>
-      <c r="N32" s="29">
-        <f>SUM(B32:M32)</f>
-        <v>94150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="B33" s="29">
-        <f>B8-B32</f>
-        <v>94385</v>
-      </c>
-      <c r="C33" s="29">
-        <f>C8-C32</f>
-        <v>1385</v>
-      </c>
-      <c r="D33" s="29">
-        <f>D8-D32</f>
-        <v>1385</v>
-      </c>
-      <c r="E33" s="29">
-        <f>E8-E32</f>
-        <v>1385</v>
-      </c>
-      <c r="F33" s="29">
-        <f>F8-F32</f>
-        <v>1385</v>
-      </c>
-      <c r="G33" s="29">
-        <f>G8-G32</f>
-        <v>1385</v>
-      </c>
-      <c r="H33" s="29">
-        <f>H8-H32</f>
-        <v>1385</v>
-      </c>
-      <c r="I33" s="29">
-        <f>I8-I32</f>
-        <v>1385</v>
-      </c>
-      <c r="J33" s="29">
-        <f>J8-J32</f>
-        <v>1385</v>
-      </c>
-      <c r="K33" s="29">
-        <f>K8-K32</f>
-        <v>1385</v>
-      </c>
-      <c r="L33" s="29" t="str">
-        <f>L8-L32</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="29" t="str">
-        <f>M8-M32</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="29">
-        <f>SUM(B33:M33)</f>
-        <v>106850</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="B34" s="29">
-        <f>0+B33</f>
-        <v>94385</v>
-      </c>
-      <c r="C34" s="29">
-        <f>B34+C33</f>
-        <v>95770</v>
-      </c>
-      <c r="D34" s="29">
-        <f>C34+D33</f>
-        <v>97155</v>
-      </c>
-      <c r="E34" s="29">
-        <f>D34+E33</f>
-        <v>98540</v>
-      </c>
-      <c r="F34" s="29">
-        <f>E34+F33</f>
-        <v>99925</v>
-      </c>
-      <c r="G34" s="29">
-        <f>F34+G33</f>
-        <v>101310</v>
-      </c>
-      <c r="H34" s="29">
-        <f>G34+H33</f>
-        <v>102695</v>
-      </c>
-      <c r="I34" s="29">
-        <f>H34+I33</f>
-        <v>104080</v>
-      </c>
-      <c r="J34" s="29">
-        <f>I34+J33</f>
-        <v>105465</v>
-      </c>
-      <c r="K34" s="29">
-        <f>J34+K33</f>
-        <v>106850</v>
-      </c>
-      <c r="L34" s="29">
-        <f>K34+L33</f>
-        <v>106850</v>
-      </c>
-      <c r="M34" s="29">
-        <f>L34+M33</f>
-        <v>106850</v>
-      </c>
-      <c r="N34" s="29">
-        <f>M34</f>
-        <v>106850</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B38" s="29">
-        <f>M34</f>
-        <v>106850</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="B39" s="26">
-        <f>MIN(B34:M34)</f>
-        <v>94385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="22"/>
+    <row r="34" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="30">
+        <f>B13+B30+B32</f>
+        <v>9790</v>
+      </c>
+      <c r="C35" s="30">
+        <f>C13+C30+C32</f>
+        <v>9790</v>
+      </c>
+      <c r="D35" s="30">
+        <f>D13+D30+D32</f>
+        <v>9790</v>
+      </c>
+      <c r="E35" s="30">
+        <f>E13+E30+E32</f>
+        <v>9790</v>
+      </c>
+      <c r="F35" s="30">
+        <f>F13+F30+F32</f>
+        <v>9790</v>
+      </c>
+      <c r="G35" s="30">
+        <f>G13+G30+G32</f>
+        <v>9790</v>
+      </c>
+      <c r="H35" s="30">
+        <f>H13+H30+H32</f>
+        <v>9790</v>
+      </c>
+      <c r="I35" s="30">
+        <f>I13+I30+I32</f>
+        <v>9790</v>
+      </c>
+      <c r="J35" s="30">
+        <f>J13+J30+J32</f>
+        <v>9790</v>
+      </c>
+      <c r="K35" s="30">
+        <f>K13+K30+K32</f>
+        <v>9790</v>
+      </c>
+      <c r="L35" s="30" t="str">
+        <f>L13+L30+L32</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="30" t="str">
+        <f>M13+M30+M32</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="30">
+        <f>SUM(B35:M35)</f>
+        <v>97900</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="30">
+        <f>B8-B35</f>
+        <v>94010</v>
+      </c>
+      <c r="C36" s="30">
+        <f>C8-C35</f>
+        <v>1010</v>
+      </c>
+      <c r="D36" s="30">
+        <f>D8-D35</f>
+        <v>1010</v>
+      </c>
+      <c r="E36" s="30">
+        <f>E8-E35</f>
+        <v>1010</v>
+      </c>
+      <c r="F36" s="30">
+        <f>F8-F35</f>
+        <v>1010</v>
+      </c>
+      <c r="G36" s="30">
+        <f>G8-G35</f>
+        <v>1010</v>
+      </c>
+      <c r="H36" s="30">
+        <f>H8-H35</f>
+        <v>1010</v>
+      </c>
+      <c r="I36" s="30">
+        <f>I8-I35</f>
+        <v>1010</v>
+      </c>
+      <c r="J36" s="30">
+        <f>J8-J35</f>
+        <v>1010</v>
+      </c>
+      <c r="K36" s="30">
+        <f>K8-K35</f>
+        <v>1010</v>
+      </c>
+      <c r="L36" s="30" t="str">
+        <f>L8-L35</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="30" t="str">
+        <f>M8-M35</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="30">
+        <f>SUM(B36:M36)</f>
+        <v>103100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="B37" s="30">
+        <f>0+B36</f>
+        <v>94010</v>
+      </c>
+      <c r="C37" s="30">
+        <f>B37+C36</f>
+        <v>95020</v>
+      </c>
+      <c r="D37" s="30">
+        <f>C37+D36</f>
+        <v>96030</v>
+      </c>
+      <c r="E37" s="30">
+        <f>D37+E36</f>
+        <v>97040</v>
+      </c>
+      <c r="F37" s="30">
+        <f>E37+F36</f>
+        <v>98050</v>
+      </c>
+      <c r="G37" s="30">
+        <f>F37+G36</f>
+        <v>99060</v>
+      </c>
+      <c r="H37" s="30">
+        <f>G37+H36</f>
+        <v>100070</v>
+      </c>
+      <c r="I37" s="30">
+        <f>H37+I36</f>
+        <v>101080</v>
+      </c>
+      <c r="J37" s="30">
+        <f>I37+J36</f>
+        <v>102090</v>
+      </c>
+      <c r="K37" s="30">
+        <f>J37+K36</f>
+        <v>103100</v>
+      </c>
+      <c r="L37" s="30">
+        <f>K37+L36</f>
+        <v>103100</v>
+      </c>
+      <c r="M37" s="30">
+        <f>L37+M36</f>
+        <v>103100</v>
+      </c>
+      <c r="N37" s="30">
+        <f>M37</f>
+        <v>103100</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="30">
+        <f>M37</f>
+        <v>103100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="27">
+        <f>MIN(B37:M37)</f>
+        <v>94010</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A44:N44"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
@@ -5042,7 +5256,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5052,645 +5266,645 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
+      <c r="B3" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>199</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="F4" s="43" t="s">
-        <v>201</v>
+      <c r="B4" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="44">
+        <v>215</v>
+      </c>
+      <c r="C7" s="45">
         <v>15</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="45">
         <v>22</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="45">
         <v>30</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="45">
         <v>36</v>
       </c>
-      <c r="G7" s="44">
+      <c r="G7" s="45">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="45">
+        <v>216</v>
+      </c>
+      <c r="C8" s="46">
         <v>201000</v>
       </c>
-      <c r="D8" s="45">
-        <v>300734.99999999994</v>
-      </c>
-      <c r="E8" s="45">
-        <v>419199.37499999994</v>
-      </c>
-      <c r="F8" s="45">
-        <v>514969.0968749998</v>
-      </c>
-      <c r="G8" s="45">
-        <v>586124.6449218749</v>
+      <c r="D8" s="46">
+        <v>300624.99999999994</v>
+      </c>
+      <c r="E8" s="46">
+        <v>418895.62499999994</v>
+      </c>
+      <c r="F8" s="46">
+        <v>514415.4843749998</v>
+      </c>
+      <c r="G8" s="46">
+        <v>585294.1417968748</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="C9" s="45">
+        <v>217</v>
+      </c>
+      <c r="C9" s="46">
         <v>64516.25</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="46">
         <v>79742.085</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="46">
         <v>82134.34754999999</v>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="46">
         <v>84598.3779765</v>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <v>87136.32931579501</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="C10" s="45">
-        <v>35550</v>
-      </c>
-      <c r="D10" s="45">
-        <v>41210.5</v>
-      </c>
-      <c r="E10" s="45">
-        <v>47815.252499999995</v>
-      </c>
-      <c r="F10" s="45">
-        <v>53325.084449999995</v>
-      </c>
-      <c r="G10" s="45">
-        <v>57646.13959287499</v>
+        <v>218</v>
+      </c>
+      <c r="C10" s="46">
+        <v>32250</v>
+      </c>
+      <c r="D10" s="46">
+        <v>41405.5</v>
+      </c>
+      <c r="E10" s="46">
+        <v>47902.6275</v>
+      </c>
+      <c r="F10" s="46">
+        <v>53302.14382499999</v>
+      </c>
+      <c r="G10" s="46">
+        <v>57510.125452249995</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="45">
-        <v>0</v>
-      </c>
-      <c r="D11" s="45">
-        <v>0</v>
-      </c>
-      <c r="E11" s="45">
-        <v>0</v>
-      </c>
-      <c r="F11" s="45">
-        <v>0</v>
-      </c>
-      <c r="G11" s="45">
+        <v>159</v>
+      </c>
+      <c r="C11" s="46">
+        <v>0</v>
+      </c>
+      <c r="D11" s="46">
+        <v>0</v>
+      </c>
+      <c r="E11" s="46">
+        <v>0</v>
+      </c>
+      <c r="F11" s="46">
+        <v>0</v>
+      </c>
+      <c r="G11" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="46">
-        <v>100933.75</v>
-      </c>
-      <c r="D12" s="46">
-        <v>179782.41499999992</v>
-      </c>
-      <c r="E12" s="46">
-        <v>289249.77494999993</v>
-      </c>
-      <c r="F12" s="46">
-        <v>377045.63444849977</v>
-      </c>
-      <c r="G12" s="46">
-        <v>441342.1760132049</v>
+      <c r="B12" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="47">
+        <v>104233.75</v>
+      </c>
+      <c r="D12" s="47">
+        <v>179477.41499999992</v>
+      </c>
+      <c r="E12" s="47">
+        <v>288858.64994999993</v>
+      </c>
+      <c r="F12" s="47">
+        <v>376514.9625734998</v>
+      </c>
+      <c r="G12" s="47">
+        <v>440647.6870288298</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="46">
-        <v>100933.75</v>
-      </c>
-      <c r="D13" s="46">
-        <v>280716.1649999999</v>
-      </c>
-      <c r="E13" s="46">
-        <v>569965.9399499998</v>
-      </c>
-      <c r="F13" s="46">
-        <v>947011.5743984996</v>
-      </c>
-      <c r="G13" s="46">
-        <v>1388353.7504117044</v>
+      <c r="B13" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="47">
+        <v>104233.75</v>
+      </c>
+      <c r="D13" s="47">
+        <v>283711.1649999999</v>
+      </c>
+      <c r="E13" s="47">
+        <v>572569.8149499998</v>
+      </c>
+      <c r="F13" s="47">
+        <v>949084.7775234997</v>
+      </c>
+      <c r="G13" s="47">
+        <v>1389732.4645523294</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C14" s="47">
-        <v>0.5021579601990049</v>
-      </c>
-      <c r="D14" s="47">
-        <v>0.5978100819658502</v>
-      </c>
-      <c r="E14" s="47">
-        <v>0.6900052628895259</v>
-      </c>
-      <c r="F14" s="47">
-        <v>0.7321713802566707</v>
-      </c>
-      <c r="G14" s="47">
-        <v>0.7529834819896233</v>
+      <c r="B14" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="48">
+        <v>0.5185758706467661</v>
+      </c>
+      <c r="D14" s="48">
+        <v>0.5970142702702701</v>
+      </c>
+      <c r="E14" s="48">
+        <v>0.68957189502755</v>
+      </c>
+      <c r="F14" s="48">
+        <v>0.7319277393660784</v>
+      </c>
+      <c r="G14" s="48">
+        <v>0.752865363859657</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="48">
+      <c r="B15" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="49">
         <v>13400</v>
       </c>
-      <c r="D15" s="48">
-        <v>13669.772727272724</v>
-      </c>
-      <c r="E15" s="48">
-        <v>13973.312499999998</v>
-      </c>
-      <c r="F15" s="48">
-        <v>14304.697135416662</v>
-      </c>
-      <c r="G15" s="48">
-        <v>14653.116123046872</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>216</v>
+      <c r="D15" s="49">
+        <v>13664.772727272724</v>
+      </c>
+      <c r="E15" s="49">
+        <v>13963.187499999998</v>
+      </c>
+      <c r="F15" s="49">
+        <v>14289.319010416662</v>
+      </c>
+      <c r="G15" s="49">
+        <v>14632.35354492187</v>
+      </c>
+      <c r="H15" s="50" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="50">
-        <v>6671.083333333333</v>
-      </c>
-      <c r="D16" s="50">
-        <v>5497.844772727273</v>
-      </c>
-      <c r="E16" s="50">
-        <v>4331.653334999999</v>
-      </c>
-      <c r="F16" s="50">
-        <v>3831.2072896249997</v>
-      </c>
-      <c r="G16" s="50">
-        <v>3619.5617227167504</v>
+      <c r="B16" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="51">
+        <v>6451.083333333333</v>
+      </c>
+      <c r="D16" s="51">
+        <v>5506.708409090909</v>
+      </c>
+      <c r="E16" s="51">
+        <v>4334.565834999999</v>
+      </c>
+      <c r="F16" s="51">
+        <v>3830.5700500416665</v>
+      </c>
+      <c r="G16" s="51">
+        <v>3616.1613692011247</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C17" s="45">
+        <v>224</v>
+      </c>
+      <c r="C17" s="46">
         <v>400</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <v>409.99999999999994</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <v>420.24999999999994</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="46">
         <v>430.75624999999985</v>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="46">
         <v>441.5251562499999</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="48">
-        <v>1720</v>
-      </c>
-      <c r="D18" s="48">
-        <v>1206.9545454545455</v>
-      </c>
-      <c r="E18" s="48">
-        <v>910.9354999999999</v>
-      </c>
-      <c r="F18" s="48">
-        <v>781.2734395833334</v>
-      </c>
-      <c r="G18" s="48">
-        <v>723.675110915625</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>220</v>
+        <v>225</v>
+      </c>
+      <c r="C18" s="49">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="49">
+        <v>1011.2727272727273</v>
+      </c>
+      <c r="E18" s="49">
+        <v>763.848</v>
+      </c>
+      <c r="F18" s="49">
+        <v>655.6362</v>
+      </c>
+      <c r="G18" s="49">
+        <v>607.7747574000001</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="51">
-        <v>6728.916666666667</v>
-      </c>
-      <c r="D19" s="51">
-        <v>8171.927954545451</v>
-      </c>
-      <c r="E19" s="51">
-        <v>9641.659164999997</v>
-      </c>
-      <c r="F19" s="51">
-        <v>10473.48984579166</v>
-      </c>
-      <c r="G19" s="51">
-        <v>11033.554400330122</v>
+      <c r="B19" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="52">
+        <v>6948.916666666667</v>
+      </c>
+      <c r="D19" s="52">
+        <v>8158.064318181815</v>
+      </c>
+      <c r="E19" s="52">
+        <v>9628.621664999997</v>
+      </c>
+      <c r="F19" s="52">
+        <v>10458.748960374995</v>
+      </c>
+      <c r="G19" s="52">
+        <v>11016.192175720746</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="47">
+      <c r="B20" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" s="48">
         <v>0.320976368159204</v>
       </c>
-      <c r="D20" s="47">
-        <v>0.2651573145792808</v>
-      </c>
-      <c r="E20" s="47">
-        <v>0.19593146471174963</v>
-      </c>
-      <c r="F20" s="47">
-        <v>0.16427855281000456</v>
-      </c>
-      <c r="G20" s="47">
-        <v>0.14866518593056174</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>223</v>
+      <c r="D20" s="48">
+        <v>0.2652543367983369</v>
+      </c>
+      <c r="E20" s="48">
+        <v>0.1960735387245928</v>
+      </c>
+      <c r="F20" s="48">
+        <v>0.16445534892730654</v>
+      </c>
+      <c r="G20" s="48">
+        <v>0.14887613439677225</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="C21" s="47">
-        <v>0.12835820895522387</v>
-      </c>
-      <c r="D21" s="47">
-        <v>0.08829368048281712</v>
-      </c>
-      <c r="E21" s="47">
-        <v>0.06519109194759654</v>
-      </c>
-      <c r="F21" s="47">
-        <v>0.05461656630597211</v>
-      </c>
-      <c r="G21" s="47">
-        <v>0.049387113624071166</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>225</v>
+      <c r="B21" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" s="48">
+        <v>0.08955223880597014</v>
+      </c>
+      <c r="D21" s="48">
+        <v>0.07400582120582122</v>
+      </c>
+      <c r="E21" s="48">
+        <v>0.05470441473338377</v>
+      </c>
+      <c r="F21" s="48">
+        <v>0.04588295632017542</v>
+      </c>
+      <c r="G21" s="48">
+        <v>0.04153636361601768</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C22" s="47">
-        <v>0.5021579601990049</v>
-      </c>
-      <c r="D22" s="47">
-        <v>0.5978100819658502</v>
-      </c>
-      <c r="E22" s="47">
-        <v>0.6900052628895259</v>
-      </c>
-      <c r="F22" s="47">
-        <v>0.7321713802566707</v>
-      </c>
-      <c r="G22" s="47">
-        <v>0.7529834819896233</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>227</v>
+      <c r="B22" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="48">
+        <v>0.5185758706467661</v>
+      </c>
+      <c r="D22" s="48">
+        <v>0.5970142702702701</v>
+      </c>
+      <c r="E22" s="48">
+        <v>0.68957189502755</v>
+      </c>
+      <c r="F22" s="48">
+        <v>0.7319277393660784</v>
+      </c>
+      <c r="G22" s="48">
+        <v>0.752865363859657</v>
+      </c>
+      <c r="H22" s="50" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="C23" s="52">
+      <c r="B23" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="53">
         <v>3</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="53">
         <v>3</v>
       </c>
-      <c r="E23" s="52">
+      <c r="E23" s="53">
         <v>3</v>
       </c>
-      <c r="F23" s="52">
+      <c r="F23" s="53">
         <v>3</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="53">
         <v>3</v>
       </c>
-      <c r="H23" s="49" t="s">
-        <v>229</v>
+      <c r="H23" s="50" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="53" t="s">
+      <c r="B24" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="53" t="s">
+      <c r="D24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="53" t="s">
+      <c r="E24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="G24" s="53" t="s">
+      <c r="G24" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="50" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="C25" s="33" t="str">
-        <f>IF('5-Year Model'!B43&gt;=0,"✓ Break-even","")</f>
+      <c r="B25" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C25" s="34" t="str">
+        <f>IF('5-Year Model'!B47&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!C43&gt;=0,'5-Year Model'!B43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!D43&gt;=0,'5-Year Model'!C43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!E43&gt;=0,'5-Year Model'!D43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="54" t="str">
-        <f>IF(AND('5-Year Model'!F43&gt;=0,'5-Year Model'!E43&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>203</v>
+      <c r="D25" s="55" t="str">
+        <f>IF(AND('5-Year Model'!C47&gt;=0,'5-Year Model'!B47&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="55" t="str">
+        <f>IF(AND('5-Year Model'!D47&gt;=0,'5-Year Model'!C47&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="55" t="str">
+        <f>IF(AND('5-Year Model'!E47&gt;=0,'5-Year Model'!D47&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="55" t="str">
+        <f>IF(AND('5-Year Model'!F47&gt;=0,'5-Year Model'!E47&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C26" s="55">
-        <v>12</v>
-      </c>
-      <c r="D26" s="52">
+      <c r="B26" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="56">
+        <v>13</v>
+      </c>
+      <c r="D26" s="53">
         <v>28</v>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="53">
         <v>53</v>
       </c>
-      <c r="F26" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="G26" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>234</v>
+      <c r="F26" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="G26" s="57" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="C27" s="52">
-        <v>368</v>
-      </c>
-      <c r="D27" s="52">
-        <v>847</v>
-      </c>
-      <c r="E27" s="52">
-        <v>1601</v>
-      </c>
-      <c r="F27" s="52">
-        <v>2506</v>
-      </c>
-      <c r="G27" s="52">
-        <v>3500</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>235</v>
+      <c r="B27" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C27" s="53">
+        <v>393</v>
+      </c>
+      <c r="D27" s="53">
+        <v>855</v>
+      </c>
+      <c r="E27" s="53">
+        <v>1607</v>
+      </c>
+      <c r="F27" s="53">
+        <v>2512</v>
+      </c>
+      <c r="G27" s="53">
+        <v>3507</v>
+      </c>
+      <c r="H27" s="50" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
+      <c r="B30" s="58" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D31" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
-        <v>246</v>
-      </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
+      <c r="B31" s="58" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D31" s="59" t="s">
+        <v>251</v>
+      </c>
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
+        <v>252</v>
+      </c>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="57" t="s">
+      <c r="B32" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D32" s="58" t="s">
-        <v>248</v>
-      </c>
-      <c r="E32" s="58"/>
-      <c r="F32" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="G32" s="59"/>
-      <c r="H32" s="59"/>
+      <c r="D32" s="59" t="s">
+        <v>254</v>
+      </c>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60" t="s">
+        <v>255</v>
+      </c>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
-        <v>250</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D33" s="58" t="s">
-        <v>251</v>
-      </c>
-      <c r="E33" s="58"/>
-      <c r="F33" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
+      <c r="B33" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D33" s="59" t="s">
+        <v>257</v>
+      </c>
+      <c r="E33" s="59"/>
+      <c r="F33" s="60" t="s">
+        <v>258</v>
+      </c>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="C34" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D34" s="58" t="s">
-        <v>254</v>
-      </c>
-      <c r="E34" s="58"/>
-      <c r="F34" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
+      <c r="B34" s="58" t="s">
+        <v>259</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" s="59"/>
+      <c r="F34" s="60" t="s">
+        <v>261</v>
+      </c>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="E35" s="58"/>
-      <c r="F35" s="59" t="s">
-        <v>258</v>
-      </c>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
+      <c r="B35" s="58" t="s">
+        <v>262</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="59" t="s">
+        <v>263</v>
+      </c>
+      <c r="E35" s="59"/>
+      <c r="F35" s="60" t="s">
+        <v>264</v>
+      </c>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
+      <c r="B37" s="58" t="s">
+        <v>265</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="60" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="60"/>
-      <c r="D39" s="60"/>
-      <c r="E39" s="60"/>
-      <c r="F39" s="60"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="60"/>
+      <c r="B39" s="61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="61"/>
+      <c r="G39" s="61"/>
+      <c r="H39" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -8,7 +8,8 @@
     <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="5-Year Model" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Year 1 Pro Forma" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Financial Health" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="Decision History" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Financial Health" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instructions'!$A1:$B37</definedName>
@@ -19,15 +20,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'5-Year Model'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Year 1 Pro Forma'!$A1:$N44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Health'!$A1:$H39</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Financial Health'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="270">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -636,6 +639,15 @@
   </si>
   <si>
     <t>Minimum Cash Month</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
   <si>
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
@@ -1042,7 +1054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1096,6 +1108,13 @@
     <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5244,6 +5263,73 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BLiberty Learning Co-Op&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -5256,7 +5342,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -5266,127 +5352,127 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="41" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
+      <c r="B3" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>207</v>
+      <c r="B4" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C7" s="45">
+        <v>218</v>
+      </c>
+      <c r="C7" s="48">
         <v>15</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="48">
         <v>22</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="48">
         <v>30</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="48">
         <v>36</v>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="48">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="C8" s="46">
+        <v>219</v>
+      </c>
+      <c r="C8" s="49">
         <v>201000</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="49">
         <v>300624.99999999994</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="49">
         <v>418895.62499999994</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="49">
         <v>514415.4843749998</v>
       </c>
-      <c r="G8" s="46">
+      <c r="G8" s="49">
         <v>585294.1417968748</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C9" s="46">
+        <v>220</v>
+      </c>
+      <c r="C9" s="49">
         <v>64516.25</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="49">
         <v>79742.085</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="49">
         <v>82134.34754999999</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="49">
         <v>84598.3779765</v>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="49">
         <v>87136.32931579501</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="46">
+        <v>221</v>
+      </c>
+      <c r="C10" s="49">
         <v>32250</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="49">
         <v>41405.5</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="49">
         <v>47902.6275</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="49">
         <v>53302.14382499999</v>
       </c>
-      <c r="G10" s="46">
+      <c r="G10" s="49">
         <v>57510.125452249995</v>
       </c>
     </row>
@@ -5394,39 +5480,39 @@
       <c r="B11" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="46">
-        <v>0</v>
-      </c>
-      <c r="D11" s="46">
-        <v>0</v>
-      </c>
-      <c r="E11" s="46">
-        <v>0</v>
-      </c>
-      <c r="F11" s="46">
-        <v>0</v>
-      </c>
-      <c r="G11" s="46">
+      <c r="C11" s="49">
+        <v>0</v>
+      </c>
+      <c r="D11" s="49">
+        <v>0</v>
+      </c>
+      <c r="E11" s="49">
+        <v>0</v>
+      </c>
+      <c r="F11" s="49">
+        <v>0</v>
+      </c>
+      <c r="G11" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C12" s="47">
+        <v>222</v>
+      </c>
+      <c r="C12" s="50">
         <v>104233.75</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="50">
         <v>179477.41499999992</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="50">
         <v>288858.64994999993</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="50">
         <v>376514.9625734998</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="50">
         <v>440647.6870288298</v>
       </c>
     </row>
@@ -5434,477 +5520,477 @@
       <c r="B13" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="50">
         <v>104233.75</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="50">
         <v>283711.1649999999</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="50">
         <v>572569.8149499998</v>
       </c>
-      <c r="F13" s="47">
+      <c r="F13" s="50">
         <v>949084.7775234997</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="50">
         <v>1389732.4645523294</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="48">
+        <v>223</v>
+      </c>
+      <c r="C14" s="51">
         <v>0.5185758706467661</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="51">
         <v>0.5970142702702701</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="51">
         <v>0.68957189502755</v>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="51">
         <v>0.7319277393660784</v>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="51">
         <v>0.752865363859657</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="49">
+        <v>224</v>
+      </c>
+      <c r="C15" s="52">
         <v>13400</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="52">
         <v>13664.772727272724</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="52">
         <v>13963.187499999998</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="52">
         <v>14289.319010416662</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="52">
         <v>14632.35354492187</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>222</v>
+      <c r="H15" s="53" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="C16" s="51">
+        <v>226</v>
+      </c>
+      <c r="C16" s="54">
         <v>6451.083333333333</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="54">
         <v>5506.708409090909</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="54">
         <v>4334.565834999999</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="54">
         <v>3830.5700500416665</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="54">
         <v>3616.1613692011247</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" s="46">
+        <v>227</v>
+      </c>
+      <c r="C17" s="49">
         <v>400</v>
       </c>
-      <c r="D17" s="46">
+      <c r="D17" s="49">
         <v>409.99999999999994</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="49">
         <v>420.24999999999994</v>
       </c>
-      <c r="F17" s="46">
+      <c r="F17" s="49">
         <v>430.75624999999985</v>
       </c>
-      <c r="G17" s="46">
+      <c r="G17" s="49">
         <v>441.5251562499999</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="C18" s="49">
+        <v>228</v>
+      </c>
+      <c r="C18" s="52">
         <v>1200</v>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="52">
         <v>1011.2727272727273</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="52">
         <v>763.848</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="52">
         <v>655.6362</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="52">
         <v>607.7747574000001</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>226</v>
+      <c r="H18" s="53" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="52">
+        <v>230</v>
+      </c>
+      <c r="C19" s="55">
         <v>6948.916666666667</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="55">
         <v>8158.064318181815</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="55">
         <v>9628.621664999997</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="55">
         <v>10458.748960374995</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="55">
         <v>11016.192175720746</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="C20" s="48">
+        <v>231</v>
+      </c>
+      <c r="C20" s="51">
         <v>0.320976368159204</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="51">
         <v>0.2652543367983369</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="51">
         <v>0.1960735387245928</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="51">
         <v>0.16445534892730654</v>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="51">
         <v>0.14887613439677225</v>
       </c>
-      <c r="H20" s="50" t="s">
-        <v>229</v>
+      <c r="H20" s="53" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="C21" s="48">
+        <v>233</v>
+      </c>
+      <c r="C21" s="51">
         <v>0.08955223880597014</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="51">
         <v>0.07400582120582122</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="51">
         <v>0.05470441473338377</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="51">
         <v>0.04588295632017542</v>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="51">
         <v>0.04153636361601768</v>
       </c>
-      <c r="H21" s="50" t="s">
-        <v>231</v>
+      <c r="H21" s="53" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="C22" s="48">
+        <v>235</v>
+      </c>
+      <c r="C22" s="51">
         <v>0.5185758706467661</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="51">
         <v>0.5970142702702701</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="51">
         <v>0.68957189502755</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="51">
         <v>0.7319277393660784</v>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="51">
         <v>0.752865363859657</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>233</v>
+      <c r="H22" s="53" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="53">
+        <v>237</v>
+      </c>
+      <c r="C23" s="56">
         <v>3</v>
       </c>
-      <c r="D23" s="53">
+      <c r="D23" s="56">
         <v>3</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="56">
         <v>3</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="56">
         <v>3</v>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="56">
         <v>3</v>
       </c>
-      <c r="H23" s="50" t="s">
-        <v>235</v>
+      <c r="H23" s="53" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C24" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="54" t="s">
+      <c r="F24" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="G24" s="54" t="s">
+      <c r="G24" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="50" t="s">
+      <c r="H24" s="53" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C25" s="34" t="str">
         <f>IF('5-Year Model'!B47&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="55" t="str">
+      <c r="D25" s="58" t="str">
         <f>IF(AND('5-Year Model'!C47&gt;=0,'5-Year Model'!B47&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="55" t="str">
+      <c r="E25" s="58" t="str">
         <f>IF(AND('5-Year Model'!D47&gt;=0,'5-Year Model'!C47&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="55" t="str">
+      <c r="F25" s="58" t="str">
         <f>IF(AND('5-Year Model'!E47&gt;=0,'5-Year Model'!D47&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="55" t="str">
+      <c r="G25" s="58" t="str">
         <f>IF(AND('5-Year Model'!F47&gt;=0,'5-Year Model'!E47&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="50" t="s">
-        <v>209</v>
+      <c r="H25" s="53" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="C26" s="56">
+        <v>241</v>
+      </c>
+      <c r="C26" s="59">
         <v>13</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="56">
         <v>28</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="56">
         <v>53</v>
       </c>
-      <c r="F26" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="G26" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>240</v>
+      <c r="F26" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="G26" s="60" t="s">
+        <v>242</v>
+      </c>
+      <c r="H26" s="53" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="56">
         <v>393</v>
       </c>
-      <c r="D27" s="53">
+      <c r="D27" s="56">
         <v>855</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="56">
         <v>1607</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="56">
         <v>2512</v>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="56">
         <v>3507</v>
       </c>
-      <c r="H27" s="50" t="s">
-        <v>241</v>
+      <c r="H27" s="53" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="58" t="s">
-        <v>246</v>
+      <c r="B30" s="61" t="s">
+        <v>249</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
+        <v>250</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>251</v>
+      </c>
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="C31" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="C31" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>251</v>
-      </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
-        <v>252</v>
-      </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
+      <c r="D31" s="62" t="s">
+        <v>254</v>
+      </c>
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="58" t="s">
-        <v>253</v>
+      <c r="B32" s="61" t="s">
+        <v>256</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D32" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="E32" s="59"/>
-      <c r="F32" s="60" t="s">
-        <v>255</v>
-      </c>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
+        <v>250</v>
+      </c>
+      <c r="D32" s="62" t="s">
+        <v>257</v>
+      </c>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="58" t="s">
-        <v>256</v>
+      <c r="B33" s="61" t="s">
+        <v>259</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="59" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="59"/>
-      <c r="F33" s="60" t="s">
-        <v>258</v>
-      </c>
-      <c r="G33" s="60"/>
-      <c r="H33" s="60"/>
+        <v>250</v>
+      </c>
+      <c r="D33" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="E33" s="62"/>
+      <c r="F33" s="63" t="s">
+        <v>261</v>
+      </c>
+      <c r="G33" s="63"/>
+      <c r="H33" s="63"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="58" t="s">
-        <v>259</v>
+      <c r="B34" s="61" t="s">
+        <v>262</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D34" s="59" t="s">
-        <v>260</v>
-      </c>
-      <c r="E34" s="59"/>
-      <c r="F34" s="60" t="s">
-        <v>261</v>
-      </c>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
+        <v>250</v>
+      </c>
+      <c r="D34" s="62" t="s">
+        <v>263</v>
+      </c>
+      <c r="E34" s="62"/>
+      <c r="F34" s="63" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
-        <v>262</v>
+      <c r="B35" s="61" t="s">
+        <v>265</v>
       </c>
       <c r="C35" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D35" s="59" t="s">
-        <v>263</v>
-      </c>
-      <c r="E35" s="59"/>
-      <c r="F35" s="60" t="s">
-        <v>264</v>
-      </c>
-      <c r="G35" s="60"/>
-      <c r="H35" s="60"/>
+        <v>250</v>
+      </c>
+      <c r="D35" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" s="62"/>
+      <c r="F35" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="58" t="s">
-        <v>265</v>
+      <c r="B37" s="61" t="s">
+        <v>268</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -38,7 +38,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -653,7 +653,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year 1 Pro Forma'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Decision History'!$A1:$H4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Decision History'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$H39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Financial Health'!$A1:$I39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Financial Health'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -38,7 +38,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -653,7 +653,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -788,7 +788,7 @@
     <t>The model reaches profit early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -5330,7 +5330,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H39"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5340,7 +5340,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>206</v>
       </c>
@@ -5350,8 +5350,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="44" t="s">
         <v>207</v>
       </c>
@@ -5361,6 +5362,7 @@
       <c r="F3" s="44"/>
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="45" t="s">
@@ -5851,7 +5853,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="12" t="s">
         <v>245</v>
       </c>
@@ -5867,8 +5869,9 @@
       </c>
       <c r="G29" s="12"/>
       <c r="H29" s="12"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="61" t="s">
         <v>249</v>
       </c>
@@ -5884,8 +5887,9 @@
       </c>
       <c r="G30" s="63"/>
       <c r="H30" s="63"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="63"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="61" t="s">
         <v>253</v>
       </c>
@@ -5901,8 +5905,9 @@
       </c>
       <c r="G31" s="63"/>
       <c r="H31" s="63"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="63"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="61" t="s">
         <v>256</v>
       </c>
@@ -5918,8 +5923,9 @@
       </c>
       <c r="G32" s="63"/>
       <c r="H32" s="63"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="63"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="61" t="s">
         <v>259</v>
       </c>
@@ -5935,8 +5941,9 @@
       </c>
       <c r="G33" s="63"/>
       <c r="H33" s="63"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="63"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="61" t="s">
         <v>262</v>
       </c>
@@ -5952,8 +5959,9 @@
       </c>
       <c r="G34" s="63"/>
       <c r="H34" s="63"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="63"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="61" t="s">
         <v>265</v>
       </c>
@@ -5969,6 +5977,7 @@
       </c>
       <c r="G35" s="63"/>
       <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" s="61" t="s">
@@ -5981,7 +5990,7 @@
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="64" t="s">
         <v>124</v>
       </c>
@@ -5991,27 +6000,28 @@
       <c r="F39" s="64"/>
       <c r="G39" s="64"/>
       <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
+++ b/artifacts/api-server/qa-output/Formula_Export_Homeschool_Co-Op_Mixed.xlsx
@@ -38,7 +38,7 @@
     <t>Liberty Learning Co-Op</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -653,7 +653,7 @@
     <t>Liberty Learning Co-Op — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
